--- a/kortdata/PU_projekt.xlsx
+++ b/kortdata/PU_projekt.xlsx
@@ -12,7 +12,6 @@
     <sheet name="Produktion" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Kolumner" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Källa och kontroll" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Frågor" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,7 +511,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Kostnad (Mkr)</t>
+          <t>Utvecklingskostnad (Mkr)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -8006,7 +8005,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Anskaffning · Utvecklingskostnad · BTA · H · Q</t>
+          <t>H · Q · BTA · Utvecklingskostnad · Anskaffning</t>
         </is>
       </c>
     </row>
@@ -8040,7 +8039,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Passera nämnden · Riskbuffert · Hållbarhetskrav · Kvalitetskrav · Tidspåverkan</t>
+          <t>BTA · Utvecklingskostnad · Anskaffning · Riskbuffert · Passera nämnden · Hållbarhetskrav · Kvalitetskrav · Tidspåverkan</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11445,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kostnad (Mkr)</t>
+          <t>Utvecklingskostnad (Mkr)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -11461,7 +11460,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tryckt under etiketten 'Anskaffning' — se Frågor</t>
+          <t>Kostnad för att ta projektet i Skede 1</t>
         </is>
       </c>
     </row>
@@ -11481,11 +11480,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Tryckt under etiketten 'Utvecklingskostnad' — se Frågor</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12212,7 +12207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12330,54 +12325,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Etiketter</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bekräftat mot fysiskt kort (BRF Eldningen): Utvecklingskostnad = CSV 'Kostnad', Anskaffning = CSV 'Anskaffning'. Textordningen i PDF:en följer inte layouten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Byggd med</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>verktyg/bygg_pu_projekt_excel.py</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Fråga</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Bakgrund</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Vilket värde står under 'Anskaffning' respektive 'Utvecklingskostnad' på framsidan?</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Textordningen i tryckfilen är 'Anskaffning, Utvecklingskostnad, BTA, 2 Mkr, 33 Mkr'. CSV har Kostnad=2 och Anskaffning=33. Om etiketterna följer värdeordningen är Anskaffning=2 och Utvecklingskostnad=33 på kortet, dvs. CSV-namnen är omvända. Behöver bekräftas mot ett fysiskt kort.</t>
         </is>
       </c>
     </row>

--- a/kortdata/PU_projekt.xlsx
+++ b/kortdata/PU_projekt.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO46"/>
+  <dimension ref="A1:AT46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -476,6 +476,11 @@
     <col width="14" customWidth="1" min="39" max="39"/>
     <col width="14" customWidth="1" min="40" max="40"/>
     <col width="14" customWidth="1" min="41" max="41"/>
+    <col width="14" customWidth="1" min="42" max="42"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
+    <col width="14" customWidth="1" min="44" max="44"/>
+    <col width="14" customWidth="1" min="45" max="45"/>
+    <col width="14" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -561,125 +566,150 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Driftnetto (Mkr/kvartal)</t>
+          <t>Driftnetto (Mkr/år)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>Räntekostnad (Mkr/år)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Lån (Mkr)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Driftnetto före ränta (Mkr/år)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>F-karaktär</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>F-motivering</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>Nivåkrav Mark</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Nivåkrav Husunderbyggnad</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Nivåkrav Stomme</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Nivåkrav Yttertak</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Nivåkrav Fasader</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Nivåkrav Stomkomplettering</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Nivåkrav Ytskikt</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Nivåkrav Installationer</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Nivåkrav Gemensamma arbeten</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Förekomst</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Formfaktor</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Linjetyp</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Antal krav</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>STA</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>KOM</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>SAM</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>NOG</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>INN</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>ABM</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Skalfaktor</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Intäkt/kvm nu</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Förslag intäkt</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Bildprompt (en)</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Antal exemplar</t>
         </is>
@@ -751,31 +781,11 @@
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr"/>
+      <c r="V2" s="2" t="inlineStr"/>
       <c r="W2" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -796,55 +806,80 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="n">
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AB2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AG2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AD2" s="2" t="inlineStr"/>
-      <c r="AE2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="n">
+      <c r="AI2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" s="2" t="inlineStr"/>
+      <c r="AQ2" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="AM2" s="2" t="n">
+      <c r="AR2" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AN2" s="2" t="inlineStr">
+      <c r="AS2" s="2" t="inlineStr">
         <is>
           <t>fire, burning flames, ember glow</t>
         </is>
       </c>
-      <c r="AO2" s="2" t="n">
+      <c r="AT2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -914,31 +949,11 @@
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr"/>
       <c r="W3" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -959,55 +974,80 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="n">
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AB3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC3" s="2" t="inlineStr">
+      <c r="AG3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AD3" s="2" t="inlineStr"/>
-      <c r="AE3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AI3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AK3" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="AL3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" s="2" t="inlineStr"/>
+      <c r="AQ3" s="2" t="n">
         <v>40.66666667</v>
       </c>
-      <c r="AM3" s="2" t="n">
+      <c r="AR3" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AN3" s="2" t="inlineStr">
+      <c r="AS3" s="2" t="inlineStr">
         <is>
           <t>forest glade, clearing, sunlight through trees</t>
         </is>
       </c>
-      <c r="AO3" s="2" t="n">
+      <c r="AT3" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1077,31 +1117,11 @@
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
       <c r="W4" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -1122,55 +1142,80 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="n">
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AB4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC4" s="2" t="inlineStr">
+      <c r="AG4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="n">
+      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AK4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" s="2" t="inlineStr"/>
+      <c r="AQ4" s="2" t="n">
         <v>39.5</v>
       </c>
-      <c r="AM4" s="2" t="n">
+      <c r="AR4" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AN4" s="2" t="inlineStr">
+      <c r="AS4" s="2" t="inlineStr">
         <is>
           <t>wide horizon, distant skyline, open sky</t>
         </is>
       </c>
-      <c r="AO4" s="2" t="n">
+      <c r="AT4" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1240,100 +1285,105 @@
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB5" s="2" t="n">
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AC5" s="2" t="inlineStr">
+      <c r="AH5" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AD5" s="2" t="n">
+      <c r="AI5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AE5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AK5" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="AL5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" s="2" t="inlineStr"/>
+      <c r="AQ5" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="AM5" s="2" t="n">
+      <c r="AR5" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="AN5" s="2" t="inlineStr">
+      <c r="AS5" s="2" t="inlineStr">
         <is>
           <t>rocky cliff, stone crag, rugged outcrop</t>
         </is>
       </c>
-      <c r="AO5" s="2" t="n">
+      <c r="AT5" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1401,102 +1451,107 @@
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X6" s="2" t="inlineStr">
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB6" s="2" t="n">
+      <c r="AF6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AC6" s="2" t="inlineStr">
+      <c r="AH6" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AD6" s="2" t="n">
+      <c r="AI6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AE6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AJ6" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AK6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="AL6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP6" s="2" t="inlineStr"/>
+      <c r="AQ6" s="2" t="n">
         <v>53.14285714</v>
       </c>
-      <c r="AM6" s="2" t="n">
+      <c r="AR6" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="AN6" s="2" t="inlineStr">
+      <c r="AS6" s="2" t="inlineStr">
         <is>
           <t>golden grain, wheat sheaf, harvest field</t>
         </is>
       </c>
-      <c r="AO6" s="2" t="n">
+      <c r="AT6" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1566,102 +1621,107 @@
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="inlineStr">
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="Z7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB7" s="2" t="n">
+      <c r="AE7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AC7" s="2" t="inlineStr">
+      <c r="AH7" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AD7" s="2" t="n">
+      <c r="AI7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AE7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AI7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AJ7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AK7" s="2" t="inlineStr"/>
-      <c r="AL7" s="2" t="n">
+      <c r="AK7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" s="2" t="inlineStr"/>
+      <c r="AQ7" s="2" t="n">
         <v>52.8</v>
       </c>
-      <c r="AM7" s="2" t="n">
+      <c r="AR7" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="AN7" s="2" t="inlineStr">
+      <c r="AS7" s="2" t="inlineStr">
         <is>
           <t>sunflower, golden petals, summer bloom</t>
         </is>
       </c>
-      <c r="AO7" s="2" t="n">
+      <c r="AT7" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1731,102 +1791,107 @@
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y8" s="2" t="inlineStr">
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="Z8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="2" t="n">
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AC8" s="2" t="inlineStr">
+      <c r="AH8" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AD8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK8" s="2" t="inlineStr"/>
-      <c r="AL8" s="2" t="n">
+      <c r="AI8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AK8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" s="2" t="inlineStr"/>
+      <c r="AQ8" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="AM8" s="2" t="n">
+      <c r="AR8" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="AN8" s="2" t="inlineStr">
+      <c r="AS8" s="2" t="inlineStr">
         <is>
           <t>reflection, mirror lake, still water</t>
         </is>
       </c>
-      <c r="AO8" s="2" t="n">
+      <c r="AT8" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1896,102 +1961,107 @@
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="inlineStr">
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC9" s="2" t="inlineStr">
+      <c r="AF9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH9" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AD9" s="2" t="n">
+      <c r="AI9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AE9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AI9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AK9" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="AL9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP9" s="2" t="inlineStr"/>
+      <c r="AQ9" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="AM9" s="2" t="n">
+      <c r="AR9" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="AN9" s="2" t="inlineStr">
+      <c r="AS9" s="2" t="inlineStr">
         <is>
           <t>forest path, winding trail, woodland walk</t>
         </is>
       </c>
-      <c r="AO9" s="2" t="n">
+      <c r="AT9" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2059,100 +2129,105 @@
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="X10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y10" s="2" t="inlineStr">
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="2" t="n">
+      <c r="AE10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AC10" s="2" t="inlineStr">
+      <c r="AH10" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AD10" s="2" t="n">
+      <c r="AI10" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AE10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AJ10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AK10" s="2" t="inlineStr"/>
-      <c r="AL10" s="2" t="n">
+      <c r="AK10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP10" s="2" t="inlineStr"/>
+      <c r="AQ10" s="2" t="n">
         <v>59.5</v>
       </c>
-      <c r="AM10" s="2" t="n">
+      <c r="AR10" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="AN10" s="2" t="inlineStr">
+      <c r="AS10" s="2" t="inlineStr">
         <is>
           <t>stone vault, arched ceiling, ancient architecture</t>
         </is>
       </c>
-      <c r="AO10" s="2" t="n">
+      <c r="AT10" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2209,7 +2284,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr">
@@ -2218,33 +2293,23 @@
         </is>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr"/>
       <c r="W11" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -2265,57 +2330,82 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="n">
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AB11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC11" s="2" t="inlineStr">
+      <c r="AG11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH11" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AD11" s="2" t="inlineStr"/>
-      <c r="AE11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AI11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AI11" s="2" t="inlineStr"/>
       <c r="AJ11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AL11" s="2" t="n">
+      <c r="AL11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ11" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AM11" s="2" t="n">
+      <c r="AR11" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AN11" s="2" t="inlineStr">
+      <c r="AS11" s="2" t="inlineStr">
         <is>
           <t>dragon lair, cave, mythical den</t>
         </is>
       </c>
-      <c r="AO11" s="2" t="n">
+      <c r="AT11" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2372,7 +2462,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr">
@@ -2381,33 +2471,23 @@
         </is>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr"/>
       <c r="W12" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -2428,57 +2508,82 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="n">
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AB12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC12" s="2" t="inlineStr">
+      <c r="AG12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH12" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AD12" s="2" t="inlineStr"/>
-      <c r="AE12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AI12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AI12" s="2" t="inlineStr"/>
       <c r="AJ12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP12" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AL12" s="2" t="n">
+      <c r="AQ12" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="AM12" s="2" t="n">
+      <c r="AR12" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AN12" s="2" t="inlineStr">
+      <c r="AS12" s="2" t="inlineStr">
         <is>
           <t>somersault, tumble, playful roll</t>
         </is>
       </c>
-      <c r="AO12" s="2" t="n">
+      <c r="AT12" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2535,7 +2640,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr">
@@ -2544,31 +2649,25 @@
         </is>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Minsta förskolan; golv på 2 Mkr så att den bär sin ränta.</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -2591,57 +2690,82 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="n">
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AB13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC13" s="2" t="inlineStr">
+      <c r="AG13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH13" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AD13" s="2" t="inlineStr"/>
-      <c r="AE13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ13" s="2" t="n">
-        <v>2</v>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AK13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP13" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AL13" s="2" t="n">
+      <c r="AQ13" s="2" t="n">
         <v>45.33333333</v>
       </c>
-      <c r="AM13" s="2" t="n">
+      <c r="AR13" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AN13" s="2" t="inlineStr">
+      <c r="AS13" s="2" t="inlineStr">
         <is>
           <t>ladybug, spotted beetle, garden friend</t>
         </is>
       </c>
-      <c r="AO13" s="2" t="n">
+      <c r="AT13" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2694,7 +2818,7 @@
         <v>3</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>179</v>
+        <v>120</v>
       </c>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr">
@@ -2703,104 +2827,119 @@
         </is>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="X14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y14" s="2" t="inlineStr">
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="Z14" s="2" t="inlineStr">
+      <c r="AE14" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB14" s="2" t="n">
+      <c r="AF14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG14" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AC14" s="2" t="inlineStr">
+      <c r="AH14" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AD14" s="2" t="n">
+      <c r="AI14" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AE14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AI14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AJ14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AL14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ14" s="2" t="n">
         <v>57.5</v>
       </c>
-      <c r="AM14" s="2" t="n">
+      <c r="AR14" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="AN14" s="2" t="inlineStr">
+      <c r="AS14" s="2" t="inlineStr">
         <is>
           <t>rainbow, colorful arc, after rain</t>
         </is>
       </c>
-      <c r="AO14" s="2" t="n">
+      <c r="AT14" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2855,7 +2994,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr">
@@ -2864,104 +3003,119 @@
         </is>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X15" s="2" t="inlineStr">
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="Y15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB15" s="2" t="n">
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AC15" s="2" t="inlineStr">
+      <c r="AH15" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AD15" s="2" t="n">
+      <c r="AI15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AE15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AJ15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AK15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AL15" s="2" t="n">
+      <c r="AL15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ15" s="2" t="n">
         <v>50.4</v>
       </c>
-      <c r="AM15" s="2" t="n">
+      <c r="AR15" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="AN15" s="2" t="inlineStr">
+      <c r="AS15" s="2" t="inlineStr">
         <is>
           <t>treasure chest, golden chest, pirate loot</t>
         </is>
       </c>
-      <c r="AO15" s="2" t="n">
+      <c r="AT15" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3014,7 +3168,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr">
@@ -3023,104 +3177,119 @@
         </is>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="X16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y16" s="2" t="inlineStr">
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="Z16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB16" s="2" t="n">
+      <c r="AE16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AC16" s="2" t="inlineStr">
+      <c r="AH16" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AD16" s="2" t="n">
+      <c r="AI16" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AE16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AI16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AJ16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AL16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ16" s="2" t="n">
         <v>54.28571429</v>
       </c>
-      <c r="AM16" s="2" t="n">
+      <c r="AR16" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="AN16" s="2" t="inlineStr">
+      <c r="AS16" s="2" t="inlineStr">
         <is>
           <t>wild strawberry patch, secret spot, hidden paradise</t>
         </is>
       </c>
-      <c r="AO16" s="2" t="n">
+      <c r="AT16" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3175,7 +3344,7 @@
         <v>1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr">
@@ -3186,41 +3355,31 @@
       <c r="Q17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>Prestige: dyr att ta fram, svagare i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -3231,59 +3390,84 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB17" s="2" t="n">
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AC17" s="2" t="inlineStr">
+      <c r="AH17" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AD17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AI17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AI17" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AJ17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AK17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP17" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AL17" s="2" t="n">
+      <c r="AQ17" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="AM17" s="2" t="n">
+      <c r="AR17" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="AN17" s="2" t="inlineStr">
+      <c r="AS17" s="2" t="inlineStr">
         <is>
           <t>star seed, cosmic sprout, celestial growth</t>
         </is>
       </c>
-      <c r="AO17" s="2" t="n">
+      <c r="AT17" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3336,7 +3520,7 @@
         <v>1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr">
@@ -3345,104 +3529,119 @@
         </is>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>Prestige: dyr att ta fram, svagare i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X18" s="2" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="Y18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="2" t="n">
+      <c r="AD18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AC18" s="2" t="inlineStr">
+      <c r="AH18" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AD18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ18" s="2" t="n">
-        <v>1</v>
+      <c r="AI18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AK18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP18" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AL18" s="2" t="n">
+      <c r="AQ18" s="2" t="n">
         <v>53.6</v>
       </c>
-      <c r="AM18" s="2" t="n">
+      <c r="AR18" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="AN18" s="2" t="inlineStr">
+      <c r="AS18" s="2" t="inlineStr">
         <is>
           <t>enchanted forest, magical woods, fairy tale grove</t>
         </is>
       </c>
-      <c r="AO18" s="2" t="n">
+      <c r="AT18" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3495,7 +3694,7 @@
         <v>1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr">
@@ -3504,104 +3703,119 @@
         </is>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="T19" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y19" s="2" t="inlineStr">
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD19" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="Z19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB19" s="2" t="n">
+      <c r="AE19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AC19" s="2" t="inlineStr">
+      <c r="AH19" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AD19" s="2" t="n">
+      <c r="AI19" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AE19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AJ19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP19" s="2" t="n">
         <v>1.05</v>
       </c>
-      <c r="AL19" s="2" t="n">
+      <c r="AQ19" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="AM19" s="2" t="n">
+      <c r="AR19" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="AN19" s="2" t="inlineStr">
+      <c r="AS19" s="2" t="inlineStr">
         <is>
           <t>coltsfoot flower, early spring bloom, yellow wildflower</t>
         </is>
       </c>
-      <c r="AO19" s="2" t="n">
+      <c r="AT19" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3658,7 +3872,7 @@
         <v>1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr">
@@ -3667,33 +3881,23 @@
         </is>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr"/>
       <c r="W20" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -3714,55 +3918,80 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="n">
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF20" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AB20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC20" s="2" t="inlineStr">
+      <c r="AG20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH20" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AD20" s="2" t="inlineStr"/>
-      <c r="AE20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AI20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AK20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AL20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ20" s="2" t="n">
         <v>46.66666667</v>
       </c>
-      <c r="AM20" s="2" t="n">
+      <c r="AR20" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AN20" s="2" t="inlineStr">
+      <c r="AS20" s="2" t="inlineStr">
         <is>
           <t>the pawn, chess piece, opening move</t>
         </is>
       </c>
-      <c r="AO20" s="2" t="n">
+      <c r="AT20" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3819,7 +4048,7 @@
         <v>1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr">
@@ -3828,33 +4057,23 @@
         </is>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr"/>
       <c r="W21" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -3875,55 +4094,80 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="n">
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF21" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AB21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC21" s="2" t="inlineStr">
+      <c r="AG21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH21" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AD21" s="2" t="inlineStr"/>
-      <c r="AE21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AK21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP21" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AL21" s="2" t="n">
+      <c r="AQ21" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AM21" s="2" t="n">
+      <c r="AR21" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AN21" s="2" t="inlineStr">
+      <c r="AS21" s="2" t="inlineStr">
         <is>
           <t>the queen, chess piece, powerful move</t>
         </is>
       </c>
-      <c r="AO21" s="2" t="n">
+      <c r="AT21" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3980,7 +4224,7 @@
         <v>1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
@@ -3989,33 +4233,23 @@
         </is>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Prestige: dyr att ta fram, svagare i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr"/>
       <c r="W22" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -4036,55 +4270,80 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="n">
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF22" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AB22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC22" s="2" t="inlineStr">
+      <c r="AG22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH22" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AD22" s="2" t="inlineStr"/>
-      <c r="AE22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AK22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP22" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AL22" s="2" t="n">
+      <c r="AQ22" s="2" t="n">
         <v>41.71428571</v>
       </c>
-      <c r="AM22" s="2" t="n">
+      <c r="AR22" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AN22" s="2" t="inlineStr">
+      <c r="AS22" s="2" t="inlineStr">
         <is>
           <t>the gambit, chess sacrifice, strategic opening</t>
         </is>
       </c>
-      <c r="AO22" s="2" t="n">
+      <c r="AT22" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4139,7 +4398,7 @@
         <v>1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr">
@@ -4148,86 +4407,82 @@
         </is>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X23" s="2" t="inlineStr">
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="Y23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z23" s="2" t="inlineStr">
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE23" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB23" s="2" t="n">
+      <c r="AF23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AC23" s="2" t="inlineStr">
+      <c r="AH23" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AD23" s="2" t="n">
+      <c r="AI23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AE23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AI23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AJ23" s="2" t="n">
         <v>1</v>
       </c>
@@ -4235,17 +4490,36 @@
         <v>1</v>
       </c>
       <c r="AL23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ23" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="AM23" s="2" t="n">
+      <c r="AR23" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="AN23" s="2" t="inlineStr">
+      <c r="AS23" s="2" t="inlineStr">
         <is>
           <t>the king, chess piece, royal protection</t>
         </is>
       </c>
-      <c r="AO23" s="2" t="n">
+      <c r="AT23" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4302,7 +4576,7 @@
         <v>1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr">
@@ -4311,104 +4585,119 @@
         </is>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB24" s="2" t="n">
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG24" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AC24" s="2" t="inlineStr">
+      <c r="AH24" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AD24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AI24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ24" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AK24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP24" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AL24" s="2" t="n">
+      <c r="AQ24" s="2" t="n">
         <v>48.8</v>
       </c>
-      <c r="AM24" s="2" t="n">
+      <c r="AR24" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="AN24" s="2" t="inlineStr">
+      <c r="AS24" s="2" t="inlineStr">
         <is>
           <t>the bishop, chess piece, diagonal move</t>
         </is>
       </c>
-      <c r="AO24" s="2" t="n">
+      <c r="AT24" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4465,7 +4754,7 @@
         <v>1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr">
@@ -4476,83 +4765,79 @@
       <c r="Q25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
+          <t>Prestige: dyr att ta fram, svagare i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB25" s="2" t="n">
-        <v>2</v>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH25" s="2" t="inlineStr">
+        <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AD25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AI25" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AJ25" s="2" t="inlineStr">
         <is>
@@ -4560,20 +4845,39 @@
         </is>
       </c>
       <c r="AK25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP25" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AL25" s="2" t="n">
+      <c r="AQ25" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="AM25" s="2" t="n">
+      <c r="AR25" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="AN25" s="2" t="inlineStr">
+      <c r="AS25" s="2" t="inlineStr">
         <is>
           <t>the countermove, chess response, defensive play</t>
         </is>
       </c>
-      <c r="AO25" s="2" t="n">
+      <c r="AT25" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4630,7 +4934,7 @@
         <v>1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr">
@@ -4639,83 +4943,81 @@
         </is>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="T26" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB26" s="2" t="n">
-        <v>1</v>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH26" s="2" t="inlineStr">
+        <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AD26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AI26" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AJ26" s="2" t="n">
         <v>1</v>
@@ -4724,17 +5026,34 @@
         <v>1</v>
       </c>
       <c r="AL26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ26" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="AM26" s="2" t="n">
+      <c r="AR26" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="AN26" s="2" t="inlineStr">
+      <c r="AS26" s="2" t="inlineStr">
         <is>
           <t>castling, chess maneuver, king safety</t>
         </is>
       </c>
-      <c r="AO26" s="2" t="n">
+      <c r="AT26" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4789,7 +5108,7 @@
         <v>3</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>181</v>
+        <v>100</v>
       </c>
       <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr">
@@ -4798,104 +5117,119 @@
         </is>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="T27" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>Prestige: dyr att ta fram, svagare i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB27" s="2" t="n">
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG27" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AC27" s="2" t="inlineStr">
+      <c r="AH27" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AD27" s="2" t="n">
+      <c r="AI27" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AE27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG27" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AJ27" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AK27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP27" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AL27" s="2" t="n">
+      <c r="AQ27" s="2" t="n">
         <v>55.5</v>
       </c>
-      <c r="AM27" s="2" t="n">
+      <c r="AR27" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="AN27" s="2" t="inlineStr">
+      <c r="AS27" s="2" t="inlineStr">
         <is>
           <t>the knight, chess piece, L-shaped move</t>
         </is>
       </c>
-      <c r="AO27" s="2" t="n">
+      <c r="AT27" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4950,7 +5284,7 @@
         <v>1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr">
@@ -4961,100 +5295,115 @@
       <c r="Q28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
+          <t>Prestige: dyr att ta fram, svagare i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X28" s="2" t="inlineStr">
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="Y28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB28" s="2" t="n">
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG28" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AC28" s="2" t="inlineStr">
+      <c r="AH28" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AD28" s="2" t="n">
+      <c r="AI28" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AE28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AJ28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AK28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP28" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AL28" s="2" t="n">
+      <c r="AQ28" s="2" t="n">
         <v>54.85714286</v>
       </c>
-      <c r="AM28" s="2" t="n">
+      <c r="AR28" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="AN28" s="2" t="inlineStr">
+      <c r="AS28" s="2" t="inlineStr">
         <is>
           <t>the rook, chess piece, straight power</t>
         </is>
       </c>
-      <c r="AO28" s="2" t="n">
+      <c r="AT28" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5109,7 +5458,7 @@
         <v>1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr">
@@ -5118,33 +5467,23 @@
         </is>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr"/>
       <c r="W29" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -5165,55 +5504,80 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="n">
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF29" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AB29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC29" s="2" t="inlineStr">
+      <c r="AG29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH29" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AD29" s="2" t="inlineStr"/>
-      <c r="AE29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ29" s="2" t="n">
-        <v>1</v>
+      <c r="AI29" s="2" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AK29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AL29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ29" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AM29" s="2" t="n">
+      <c r="AR29" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AN29" s="2" t="inlineStr">
+      <c r="AS29" s="2" t="inlineStr">
         <is>
           <t>galaxy, spiral nebula, cosmic swirl</t>
         </is>
       </c>
-      <c r="AO29" s="2" t="n">
+      <c r="AT29" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5268,7 +5632,7 @@
         <v>1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr">
@@ -5277,33 +5641,23 @@
         </is>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr"/>
       <c r="W30" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -5324,55 +5678,80 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="n">
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AB30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC30" s="2" t="inlineStr">
+      <c r="AG30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH30" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AD30" s="2" t="inlineStr"/>
-      <c r="AE30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ30" s="2" t="n">
-        <v>1</v>
+      <c r="AI30" s="2" t="inlineStr"/>
+      <c r="AJ30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AK30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP30" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AL30" s="2" t="n">
+      <c r="AQ30" s="2" t="n">
         <v>43.33333333</v>
       </c>
-      <c r="AM30" s="2" t="n">
+      <c r="AR30" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AN30" s="2" t="inlineStr">
+      <c r="AS30" s="2" t="inlineStr">
         <is>
           <t>lighthouse, beacon tower, guiding light</t>
         </is>
       </c>
-      <c r="AO30" s="2" t="n">
+      <c r="AT30" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5427,7 +5806,7 @@
         <v>1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr">
@@ -5438,31 +5817,21 @@
       <c r="Q31" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr"/>
       <c r="W31" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -5483,55 +5852,80 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="n">
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF31" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AB31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC31" s="2" t="inlineStr">
+      <c r="AG31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH31" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AD31" s="2" t="inlineStr"/>
-      <c r="AE31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ31" s="2" t="n">
-        <v>1</v>
+      <c r="AI31" s="2" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AK31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP31" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AL31" s="2" t="n">
+      <c r="AQ31" s="2" t="n">
         <v>41.5</v>
       </c>
-      <c r="AM31" s="2" t="n">
+      <c r="AR31" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AN31" s="2" t="inlineStr">
+      <c r="AS31" s="2" t="inlineStr">
         <is>
           <t>bastion, fortified tower, stronghold</t>
         </is>
       </c>
-      <c r="AO31" s="2" t="n">
+      <c r="AT31" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5588,7 +5982,7 @@
         <v>1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr">
@@ -5597,104 +5991,119 @@
         </is>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="X32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB32" s="2" t="n">
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AC32" s="2" t="inlineStr">
+      <c r="AH32" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AD32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ32" s="2" t="n">
-        <v>1</v>
+      <c r="AI32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AK32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AL32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ32" s="2" t="n">
         <v>48.8</v>
       </c>
-      <c r="AM32" s="2" t="n">
+      <c r="AR32" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="AN32" s="2" t="inlineStr">
+      <c r="AS32" s="2" t="inlineStr">
         <is>
           <t>nebula, cosmic cloud, star nursery</t>
         </is>
       </c>
-      <c r="AO32" s="2" t="n">
+      <c r="AT32" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5749,113 +6158,132 @@
         <v>1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Tvilling med Kometbanan i Projektutvecklingen, men C i stället för D — samma pris, bättre förvaltning.</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X33" s="2" t="inlineStr">
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="Y33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB33" s="2" t="n">
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG33" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AC33" s="2" t="inlineStr">
+      <c r="AH33" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AD33" s="2" t="n">
+      <c r="AI33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AE33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ33" s="2" t="n">
-        <v>1</v>
+      <c r="AJ33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AK33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP33" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AL33" s="2" t="n">
+      <c r="AQ33" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="AM33" s="2" t="n">
+      <c r="AR33" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="AN33" s="2" t="inlineStr">
+      <c r="AS33" s="2" t="inlineStr">
         <is>
           <t>quadrant, navigation instrument, star chart</t>
         </is>
       </c>
-      <c r="AO33" s="2" t="n">
+      <c r="AT33" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5910,7 +6338,7 @@
         <v>1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr">
@@ -5921,100 +6349,115 @@
       <c r="Q34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
+          <t>Prestige: dyr att ta fram, svagare i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="X34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y34" s="2" t="inlineStr">
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD34" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="Z34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB34" s="2" t="n">
+      <c r="AE34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG34" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AC34" s="2" t="inlineStr">
+      <c r="AH34" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AD34" s="2" t="n">
+      <c r="AI34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AE34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AJ34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AK34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP34" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AL34" s="2" t="n">
+      <c r="AQ34" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="AM34" s="2" t="n">
+      <c r="AR34" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="AN34" s="2" t="inlineStr">
+      <c r="AS34" s="2" t="inlineStr">
         <is>
           <t>comet path, orbital trail, stellar trajectory</t>
         </is>
       </c>
-      <c r="AO34" s="2" t="n">
+      <c r="AT34" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6069,7 +6512,7 @@
         <v>4</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr">
@@ -6078,104 +6521,119 @@
         </is>
       </c>
       <c r="Q35" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="X35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y35" s="2" t="inlineStr">
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD35" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="Z35" s="2" t="inlineStr">
+      <c r="AE35" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB35" s="2" t="n">
+      <c r="AF35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG35" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AC35" s="2" t="inlineStr">
+      <c r="AH35" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AD35" s="2" t="n">
+      <c r="AI35" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AE35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ35" s="2" t="n">
-        <v>1</v>
+      <c r="AJ35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AK35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AL35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ35" s="2" t="n">
         <v>58.5</v>
       </c>
-      <c r="AM35" s="2" t="n">
+      <c r="AR35" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="AN35" s="2" t="inlineStr">
+      <c r="AS35" s="2" t="inlineStr">
         <is>
           <t>star harbor, celestial port, cosmic dock</t>
         </is>
       </c>
-      <c r="AO35" s="2" t="n">
+      <c r="AT35" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6230,7 +6688,7 @@
         <v>3</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>182</v>
+        <v>100</v>
       </c>
       <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr">
@@ -6239,33 +6697,23 @@
         </is>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Prestige: dyr att ta fram, svagare i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr"/>
       <c r="W36" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -6273,68 +6721,93 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="Y36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE36" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB36" s="2" t="n">
+      <c r="AF36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG36" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AC36" s="2" t="inlineStr">
+      <c r="AH36" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AD36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AI36" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AJ36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AK36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP36" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AL36" s="2" t="n">
+      <c r="AQ36" s="2" t="n">
         <v>55.5</v>
       </c>
-      <c r="AM36" s="2" t="n">
+      <c r="AR36" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="AN36" s="2" t="inlineStr">
+      <c r="AS36" s="2" t="inlineStr">
         <is>
           <t>space axis, cosmic alignment, stellar center</t>
         </is>
       </c>
-      <c r="AO36" s="2" t="n">
+      <c r="AT36" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6389,7 +6862,7 @@
         <v>4</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>205</v>
+        <v>120</v>
       </c>
       <c r="O37" s="2" t="inlineStr"/>
       <c r="P37" s="2" t="inlineStr">
@@ -6398,33 +6871,23 @@
         </is>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr"/>
       <c r="W37" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -6445,57 +6908,82 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB37" s="2" t="n">
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG37" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AC37" s="2" t="inlineStr">
+      <c r="AH37" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AD37" s="2" t="n">
+      <c r="AI37" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AE37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG37" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH37" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ37" s="2" t="n">
-        <v>1</v>
+      <c r="AJ37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AK37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP37" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AL37" s="2" t="n">
+      <c r="AQ37" s="2" t="n">
         <v>59.5</v>
       </c>
-      <c r="AM37" s="2" t="n">
+      <c r="AR37" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="AN37" s="2" t="inlineStr">
+      <c r="AS37" s="2" t="inlineStr">
         <is>
           <t>observatory, telescope dome, stargazing</t>
         </is>
       </c>
-      <c r="AO37" s="2" t="n">
+      <c r="AT37" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6552,7 +7040,7 @@
         <v>1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr">
@@ -6563,29 +7051,23 @@
       <c r="Q38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="T38" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Instegsprojektet som blir spelets kassako i förvaltningen — låg yield på bostäder.</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -6608,57 +7090,82 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="n">
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AB38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC38" s="2" t="inlineStr">
+      <c r="AG38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH38" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AD38" s="2" t="inlineStr"/>
-      <c r="AE38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AI38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ38" s="2" t="n">
-        <v>1</v>
+      <c r="AI38" s="2" t="inlineStr"/>
+      <c r="AJ38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AK38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AL38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ38" s="2" t="n">
         <v>45.33333333</v>
       </c>
-      <c r="AM38" s="2" t="n">
+      <c r="AR38" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AN38" s="2" t="inlineStr">
+      <c r="AS38" s="2" t="inlineStr">
         <is>
           <t>harbor change, port transition, dock shift</t>
         </is>
       </c>
-      <c r="AO38" s="2" t="n">
+      <c r="AT38" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6715,7 +7222,7 @@
         <v>1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr">
@@ -6726,31 +7233,21 @@
       <c r="Q39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="T39" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr"/>
       <c r="W39" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -6771,57 +7268,82 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="n">
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AB39" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
+      <c r="AG39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH39" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AD39" s="2" t="inlineStr"/>
-      <c r="AE39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG39" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AI39" s="2" t="inlineStr"/>
       <c r="AJ39" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="AK39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP39" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AL39" s="2" t="n">
+      <c r="AQ39" s="2" t="n">
         <v>42.4</v>
       </c>
-      <c r="AM39" s="2" t="n">
+      <c r="AR39" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AN39" s="2" t="inlineStr">
+      <c r="AS39" s="2" t="inlineStr">
         <is>
           <t>birdsong, avian melody, morning chorus</t>
         </is>
       </c>
-      <c r="AO39" s="2" t="n">
+      <c r="AT39" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6878,7 +7400,7 @@
         <v>1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr">
@@ -6887,106 +7409,121 @@
         </is>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S40" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="T40" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA40" s="2" t="n">
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AB40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC40" s="2" t="inlineStr">
+      <c r="AG40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH40" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AD40" s="2" t="n">
+      <c r="AI40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AE40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AI40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ40" s="2" t="n">
-        <v>1</v>
+      <c r="AJ40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AK40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP40" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AL40" s="2" t="n">
+      <c r="AQ40" s="2" t="n">
         <v>47.33333333</v>
       </c>
-      <c r="AM40" s="2" t="n">
+      <c r="AR40" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="AN40" s="2" t="inlineStr">
+      <c r="AS40" s="2" t="inlineStr">
         <is>
           <t>mountain slope, hillside, rocky incline</t>
         </is>
       </c>
-      <c r="AO40" s="2" t="n">
+      <c r="AT40" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7041,7 +7578,7 @@
         <v>1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr">
@@ -7052,29 +7589,23 @@
       <c r="Q41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="T41" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Liten hyresrätt; dämpad så att inte alla små hyresrätter blir kassakor.</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -7084,72 +7615,97 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="Y41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA41" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC41" s="2" t="inlineStr">
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH41" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AD41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG41" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK41" s="2" t="n">
-        <v>1</v>
+      <c r="AI41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AK41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AL41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ41" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="AM41" s="2" t="n">
+      <c r="AR41" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="AN41" s="2" t="inlineStr">
+      <c r="AS41" s="2" t="inlineStr">
         <is>
           <t>rose grove, flowering garden, romantic park</t>
         </is>
       </c>
-      <c r="AO41" s="2" t="n">
+      <c r="AT41" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7204,7 +7760,7 @@
         <v>1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr">
@@ -7213,106 +7769,121 @@
         </is>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="T42" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr"/>
       <c r="W42" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB42" s="2" t="n">
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AC42" s="2" t="inlineStr">
+      <c r="AH42" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AD42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AI42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ42" s="2" t="n">
-        <v>1</v>
+      <c r="AI42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AK42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP42" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AL42" s="2" t="n">
+      <c r="AQ42" s="2" t="n">
         <v>49.6</v>
       </c>
-      <c r="AM42" s="2" t="n">
+      <c r="AR42" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="AN42" s="2" t="inlineStr">
+      <c r="AS42" s="2" t="inlineStr">
         <is>
           <t>leaf meadow, deciduous clearing, green pasture</t>
         </is>
       </c>
-      <c r="AO42" s="2" t="n">
+      <c r="AT42" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7367,7 +7938,7 @@
         <v>1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr">
@@ -7378,102 +7949,117 @@
       <c r="Q43" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
+      <c r="R43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="T43" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z43" s="2" t="inlineStr">
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE43" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB43" s="2" t="n">
+      <c r="AF43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG43" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AC43" s="2" t="inlineStr">
+      <c r="AH43" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AD43" s="2" t="n">
+      <c r="AI43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AE43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AI43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AJ43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AK43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP43" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AL43" s="2" t="n">
+      <c r="AQ43" s="2" t="n">
         <v>51.33333333</v>
       </c>
-      <c r="AM43" s="2" t="n">
+      <c r="AR43" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="AN43" s="2" t="inlineStr">
+      <c r="AS43" s="2" t="inlineStr">
         <is>
           <t>mill hill, grinding slope, water mill</t>
         </is>
       </c>
-      <c r="AO43" s="2" t="n">
+      <c r="AT43" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7528,7 +8114,7 @@
         <v>1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr">
@@ -7539,102 +8125,121 @@
       <c r="Q44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
+      <c r="R44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="T44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Liten hyresrätt; dämpad så att inte alla små hyresrätter blir kassakor.</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z44" s="2" t="inlineStr">
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE44" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC44" s="2" t="inlineStr">
+      <c r="AF44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH44" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AD44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ44" s="2" t="n">
-        <v>1</v>
+      <c r="AI44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AK44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AL44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ44" s="2" t="n">
         <v>50.66666667</v>
       </c>
-      <c r="AM44" s="2" t="n">
+      <c r="AR44" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="AN44" s="2" t="inlineStr">
+      <c r="AS44" s="2" t="inlineStr">
         <is>
           <t>river bank, stream edge, waterside</t>
         </is>
       </c>
-      <c r="AO44" s="2" t="n">
+      <c r="AT44" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7687,7 +8292,7 @@
         <v>4</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr">
@@ -7696,104 +8301,119 @@
         </is>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S45" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="T45" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="X45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y45" s="2" t="inlineStr">
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD45" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="Z45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB45" s="2" t="n">
+      <c r="AE45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG45" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AC45" s="2" t="inlineStr">
+      <c r="AH45" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AD45" s="2" t="n">
+      <c r="AI45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AE45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG45" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AI45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AJ45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AK45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP45" s="2" t="n">
         <v>1.05</v>
       </c>
-      <c r="AL45" s="2" t="n">
+      <c r="AQ45" s="2" t="n">
         <v>56.5</v>
       </c>
-      <c r="AM45" s="2" t="n">
+      <c r="AR45" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="AN45" s="2" t="inlineStr">
+      <c r="AS45" s="2" t="inlineStr">
         <is>
           <t>stone edge, rock ridge, granite brow</t>
         </is>
       </c>
-      <c r="AO45" s="2" t="n">
+      <c r="AT45" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7846,113 +8466,132 @@
         <v>1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="O46" s="2" t="inlineStr"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Q46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R46" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="T46" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Stort hållbart projekt; C i stället för D (texten nämner ingen energiklass).</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z46" s="2" t="inlineStr">
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE46" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB46" s="2" t="n">
+      <c r="AF46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG46" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AC46" s="2" t="inlineStr">
+      <c r="AH46" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AD46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ46" s="2" t="n">
-        <v>1</v>
+      <c r="AI46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AK46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP46" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AL46" s="2" t="n">
+      <c r="AQ46" s="2" t="n">
         <v>53.71428571</v>
       </c>
-      <c r="AM46" s="2" t="n">
+      <c r="AR46" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="AN46" s="2" t="inlineStr">
+      <c r="AS46" s="2" t="inlineStr">
         <is>
           <t>lake glimmer, water sparkle, shimmering shore</t>
         </is>
       </c>
-      <c r="AO46" s="2" t="n">
+      <c r="AT46" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8073,7 +8712,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KÖP OCH SÄLJ FÖRVALTNING</t>
+          <t>FÖRVALTNING</t>
         </is>
       </c>
     </row>
@@ -8090,7 +8729,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aktuellt marknadsvärde · Driftnetto / Yield · Driftnetto · Energiklass · /kvartal</t>
+          <t>Driftnetto · Räntekostnad · Lån · Marknadsvärde · Energiklass · Mkr/år</t>
         </is>
       </c>
     </row>
@@ -8107,7 +8746,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Min. accepterat bud: 80 % av marknadsvärde</t>
+          <t>Marknadsvärde = (driftnetto + ränta) ÷ yield</t>
         </is>
       </c>
     </row>
@@ -8124,7 +8763,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kontantinsats: 30 % av köpeskillingen</t>
+          <t>Marknadsvärde under lånet → tvångsförsäljning</t>
         </is>
       </c>
     </row>
@@ -11279,7 +11918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -11600,7 +12239,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BRF: försäljningspris. Övriga: NYTT — MV vid startyield = driftnetto före ränta ÷ yield (bostäder 4 %, övriga 5 %)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11642,19 +12285,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tryckt endast på förvaltningsbara typer (ej BRF)</t>
+          <t>Ej BRF. NYTT värde för omtrycket (Kvadranten och Sjöglimten D → C)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Driftnetto (Mkr/kvartal)</t>
+          <t>Driftnetto (Mkr/år)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Driftnetto</t>
+          <t>F_DN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -11664,19 +12307,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tryckt endast på förvaltningsbara typer (ej BRF)</t>
+          <t>NYTT. Ej BRF. Efter ränta, vid kortets energiklass. Kan vara 0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nivåkrav Mark</t>
+          <t>Räntekostnad (Mkr/år)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MARK</t>
+          <t>F_ranta</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -11686,19 +12329,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>'-' = inget krav</t>
+          <t>NYTT. Ej BRF. 3 % av lånet, fast i grundspelet</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nivåkrav Husunderbyggnad</t>
+          <t>Lån (Mkr)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HUSUNDERBYGGNAD</t>
+          <t>F_lan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -11708,85 +12351,85 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>'-' = inget krav</t>
+          <t>NYTT. Ej BRF. 70 % av MV vid start, avrundat till 10</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nivåkrav Stomme</t>
+          <t>Driftnetto före ränta (Mkr/år)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>STOMME</t>
+          <t>F_noi</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nej</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>'-' = inget krav</t>
+          <t>Ej tryckt — = driftnetto + ränta; styr MV</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nivåkrav Yttertak</t>
+          <t>F-karaktär</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>YTTERTAK</t>
+          <t>F_karaktar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nej</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>'-' = inget krav</t>
+          <t>Ej tryckt — MV/anskaffning: kassako ≥ 1,25, prestige ≤ 0,85</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nivåkrav Fasader</t>
+          <t>F-motivering</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FASADER</t>
+          <t>F_motivering</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nej</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>'-' = inget krav</t>
+          <t>Ej tryckt — avsiktliga avsteg från grundregeln</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nivåkrav Stomkomplettering</t>
+          <t>Nivåkrav Mark</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>STOMKOMPLETTERING</t>
+          <t>MARK</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -11803,12 +12446,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nivåkrav Ytskikt</t>
+          <t>Nivåkrav Husunderbyggnad</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>INV YTSKIKT</t>
+          <t>HUSUNDERBYGGNAD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -11825,12 +12468,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nivåkrav Installationer</t>
+          <t>Nivåkrav Stomme</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>INSTALLATIONER</t>
+          <t>STOMME</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -11847,12 +12490,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nivåkrav Gemensamma arbeten</t>
+          <t>Nivåkrav Yttertak</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GEMENSAMMA ARBETEN</t>
+          <t>YTTERTAK</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -11869,122 +12512,122 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Förekomst</t>
+          <t>Nivåkrav Fasader</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Förekomst</t>
+          <t>FASADER</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nej</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ej tryckt — speldata</t>
+          <t>'-' = inget krav</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Formfaktor</t>
+          <t>Nivåkrav Stomkomplettering</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Formfaktor</t>
+          <t>STOMKOMPLETTERING</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nej</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ej tryckt — styr brickans form (1–8)</t>
+          <t>'-' = inget krav</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Linjetyp</t>
+          <t>Nivåkrav Ytskikt</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>linjetyp</t>
+          <t>INV YTSKIKT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nej</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ej tryckt — ramens linjestil</t>
+          <t>'-' = inget krav</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Antal krav</t>
+          <t>Nivåkrav Installationer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Antal krav</t>
+          <t>INSTALLATIONER</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nej</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ej tryckt</t>
+          <t>'-' = inget krav</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>Nivåkrav Gemensamma arbeten</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>GEMENSAMMA ARBETEN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nej</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ej tryckt — kompetens</t>
+          <t>'-' = inget krav</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KOM</t>
+          <t>Förekomst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KOM</t>
+          <t>Förekomst</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -11994,19 +12637,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ej tryckt — kompetens</t>
+          <t>Ej tryckt — speldata</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>Formfaktor</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>Formfaktor</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -12016,19 +12659,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ej tryckt — kompetens</t>
+          <t>Ej tryckt — styr brickans form (1–8)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NOG</t>
+          <t>Linjetyp</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NOG</t>
+          <t>linjetyp</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -12038,19 +12681,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ej tryckt — kompetens</t>
+          <t>Ej tryckt — ramens linjestil</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>INN</t>
+          <t>Antal krav</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>INN</t>
+          <t>Antal krav</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -12060,19 +12703,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ej tryckt — kompetens</t>
+          <t>Ej tryckt</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ABM</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ABM</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -12089,12 +12732,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Skalfaktor</t>
+          <t>KOM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Skalfaktor</t>
+          <t>KOM</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -12104,19 +12747,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ej tryckt</t>
+          <t>Ej tryckt — kompetens</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Intäkt/kvm nu</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>intäkt/kvm nu</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -12126,19 +12769,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ej tryckt — beräkningsunderlag</t>
+          <t>Ej tryckt — kompetens</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Förslag intäkt</t>
+          <t>NOG</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>förslag intäkt</t>
+          <t>NOG</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -12148,19 +12791,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ej tryckt — beräkningsunderlag</t>
+          <t>Ej tryckt — kompetens</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bildprompt (en)</t>
+          <t>INN</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>namn_en</t>
+          <t>INN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -12170,27 +12813,137 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ej tryckt — underlag för bildgenerering</t>
+          <t>Ej tryckt — kompetens</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>ABM</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ABM</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Ej tryckt — kompetens</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Skalfaktor</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Skalfaktor</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Ej tryckt</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Intäkt/kvm nu</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>intäkt/kvm nu</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Ej tryckt — beräkningsunderlag</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Förslag intäkt</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>förslag intäkt</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Ej tryckt — beräkningsunderlag</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Bildprompt (en)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>namn_en</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Ej tryckt — underlag för bildgenerering</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>Antal exemplar</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Nej</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Antal tryckta kort (utskrift_config: 1)</t>
         </is>
@@ -12207,7 +12960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12349,10 +13102,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Omtryck</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Marknadsvärde, energiklass, driftnetto (nu efter ränta, per år), räntekostnad och lån för förvaltningsbara typer kommer från data/forvaltning_2-1/F2-1_projektkort.csv — de tryckta värdena finns kvar i arv/ och i tryckfilens text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Byggd med</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>verktyg/bygg_pu_projekt_excel.py</t>
         </is>

--- a/kortdata/PU_projekt.xlsx
+++ b/kortdata/PU_projekt.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT46"/>
+  <dimension ref="A1:AV46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -481,6 +481,8 @@
     <col width="14" customWidth="1" min="44" max="44"/>
     <col width="14" customWidth="1" min="45" max="45"/>
     <col width="14" customWidth="1" min="46" max="46"/>
+    <col width="14" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -641,75 +643,85 @@
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
+          <t>Antal rutor</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Form (rutor)</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>Förekomst</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Formfaktor</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Linjetyp</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Antal krav</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>STA</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>KOM</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>SAM</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>NOG</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>INN</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>ABM</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Skalfaktor</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Intäkt/kvm nu</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Förslag intäkt</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Bildprompt (en)</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Antal exemplar</t>
         </is>
@@ -832,32 +844,32 @@
         </is>
       </c>
       <c r="AF2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [1, 0], [1, 1], [1, 2]]</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AG2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH2" s="2" t="inlineStr">
+      <c r="AI2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AK2" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="AK2" s="2" t="inlineStr"/>
       <c r="AL2" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="AM2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN2" s="2" t="inlineStr">
         <is>
@@ -867,19 +879,27 @@
       <c r="AO2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP2" s="2" t="inlineStr"/>
+      <c r="AP2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AQ2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR2" s="2" t="inlineStr"/>
+      <c r="AS2" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="AR2" s="2" t="n">
+      <c r="AT2" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AS2" s="2" t="inlineStr">
+      <c r="AU2" s="2" t="inlineStr">
         <is>
           <t>fire, burning flames, ember glow</t>
         </is>
       </c>
-      <c r="AT2" s="2" t="n">
+      <c r="AV2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1000,54 +1020,62 @@
         </is>
       </c>
       <c r="AF3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG3" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [1, 0], [1, 1], [2, 0], [2, 1], [3, 1]]</t>
+        </is>
+      </c>
+      <c r="AH3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AG3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr">
+      <c r="AI3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ3" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AK3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AN3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP3" s="2" t="inlineStr"/>
+      <c r="AK3" s="2" t="inlineStr"/>
+      <c r="AL3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AQ3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" s="2" t="inlineStr"/>
+      <c r="AS3" s="2" t="n">
         <v>40.66666667</v>
       </c>
-      <c r="AR3" s="2" t="n">
+      <c r="AT3" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AS3" s="2" t="inlineStr">
+      <c r="AU3" s="2" t="inlineStr">
         <is>
           <t>forest glade, clearing, sunlight through trees</t>
         </is>
       </c>
-      <c r="AT3" s="2" t="n">
+      <c r="AV3" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1168,32 +1196,32 @@
         </is>
       </c>
       <c r="AF4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [1, 1], [2, 0], [2, 1], [3, 0], [3, 1]]</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AG4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH4" s="2" t="inlineStr">
+      <c r="AI4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AK4" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="AK4" s="2" t="inlineStr"/>
       <c r="AL4" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="AM4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN4" s="2" t="inlineStr">
         <is>
@@ -1203,19 +1231,27 @@
       <c r="AO4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP4" s="2" t="inlineStr"/>
+      <c r="AP4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AQ4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" s="2" t="inlineStr"/>
+      <c r="AS4" s="2" t="n">
         <v>39.5</v>
       </c>
-      <c r="AR4" s="2" t="n">
+      <c r="AT4" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AS4" s="2" t="inlineStr">
+      <c r="AU4" s="2" t="inlineStr">
         <is>
           <t>wide horizon, distant skyline, open sky</t>
         </is>
       </c>
-      <c r="AT4" s="2" t="n">
+      <c r="AV4" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1336,54 +1372,62 @@
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG5" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [1, 1], [2, 0], [2, 1]]</t>
+        </is>
+      </c>
+      <c r="AH5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AH5" s="2" t="inlineStr">
+      <c r="AJ5" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AI5" s="2" t="n">
+      <c r="AK5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AJ5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AK5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" s="2" t="n">
-        <v>1</v>
+      <c r="AL5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AM5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AN5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AN5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AO5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP5" s="2" t="inlineStr"/>
+      <c r="AP5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AQ5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" s="2" t="inlineStr"/>
+      <c r="AS5" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="AR5" s="2" t="n">
+      <c r="AT5" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="AS5" s="2" t="inlineStr">
+      <c r="AU5" s="2" t="inlineStr">
         <is>
           <t>rocky cliff, stone crag, rugged outcrop</t>
         </is>
       </c>
-      <c r="AT5" s="2" t="n">
+      <c r="AV5" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1502,56 +1546,64 @@
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG6" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG6" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [2, 0], [3, 0], [4, 0], [4, 1]]</t>
+        </is>
+      </c>
+      <c r="AH6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AH6" s="2" t="inlineStr">
+      <c r="AJ6" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AI6" s="2" t="n">
+      <c r="AK6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AJ6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AK6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL6" s="2" t="n">
-        <v>1</v>
+      <c r="AL6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AM6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP6" s="2" t="inlineStr"/>
-      <c r="AQ6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR6" s="2" t="inlineStr"/>
+      <c r="AS6" s="2" t="n">
         <v>53.14285714</v>
       </c>
-      <c r="AR6" s="2" t="n">
+      <c r="AT6" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="AS6" s="2" t="inlineStr">
+      <c r="AU6" s="2" t="inlineStr">
         <is>
           <t>golden grain, wheat sheaf, harvest field</t>
         </is>
       </c>
-      <c r="AT6" s="2" t="n">
+      <c r="AV6" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1672,56 +1724,64 @@
         </is>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG7" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [1, 0], [1, 1], [2, 0], [2, 1]]</t>
+        </is>
+      </c>
+      <c r="AH7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AH7" s="2" t="inlineStr">
+      <c r="AJ7" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AI7" s="2" t="n">
+      <c r="AK7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AJ7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AL7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AN7" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AO7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AQ7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" s="2" t="inlineStr"/>
+      <c r="AS7" s="2" t="n">
         <v>52.8</v>
       </c>
-      <c r="AR7" s="2" t="n">
+      <c r="AT7" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="AS7" s="2" t="inlineStr">
+      <c r="AU7" s="2" t="inlineStr">
         <is>
           <t>sunflower, golden petals, summer bloom</t>
         </is>
       </c>
-      <c r="AT7" s="2" t="n">
+      <c r="AV7" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1842,26 +1902,26 @@
         </is>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AH8" s="2" t="inlineStr">
+      <c r="AG8" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 1], [2, 1]]</t>
+        </is>
+      </c>
+      <c r="AH8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ8" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AI8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AK8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL8" s="2" t="inlineStr">
         <is>
@@ -1869,7 +1929,7 @@
         </is>
       </c>
       <c r="AM8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN8" s="2" t="inlineStr">
         <is>
@@ -1877,21 +1937,29 @@
         </is>
       </c>
       <c r="AO8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP8" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AP8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AQ8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" s="2" t="inlineStr"/>
+      <c r="AS8" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="AR8" s="2" t="n">
+      <c r="AT8" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="AS8" s="2" t="inlineStr">
+      <c r="AU8" s="2" t="inlineStr">
         <is>
           <t>reflection, mirror lake, still water</t>
         </is>
       </c>
-      <c r="AT8" s="2" t="n">
+      <c r="AV8" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2012,56 +2080,64 @@
         </is>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH9" s="2" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="AG9" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [0, 2]]</t>
+        </is>
+      </c>
+      <c r="AH9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ9" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AI9" s="2" t="n">
+      <c r="AK9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AJ9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AK9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AN9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP9" s="2" t="inlineStr"/>
+      <c r="AL9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AQ9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR9" s="2" t="inlineStr"/>
+      <c r="AS9" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="AR9" s="2" t="n">
+      <c r="AT9" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="AS9" s="2" t="inlineStr">
+      <c r="AU9" s="2" t="inlineStr">
         <is>
           <t>forest path, winding trail, woodland walk</t>
         </is>
       </c>
-      <c r="AT9" s="2" t="n">
+      <c r="AV9" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2180,32 +2256,32 @@
         </is>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AH10" s="2" t="inlineStr">
+      <c r="AG10" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [0, 2], [0, 3], [1, 2], [1, 3], [2, 3], [3, 3]]</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ10" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AI10" s="2" t="n">
+      <c r="AK10" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AJ10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AL10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AM10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN10" s="2" t="inlineStr">
         <is>
@@ -2215,19 +2291,27 @@
       <c r="AO10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP10" s="2" t="inlineStr"/>
+      <c r="AP10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AQ10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" s="2" t="inlineStr"/>
+      <c r="AS10" s="2" t="n">
         <v>59.5</v>
       </c>
-      <c r="AR10" s="2" t="n">
+      <c r="AT10" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="AS10" s="2" t="inlineStr">
+      <c r="AU10" s="2" t="inlineStr">
         <is>
           <t>stone vault, arched ceiling, ancient architecture</t>
         </is>
       </c>
-      <c r="AT10" s="2" t="n">
+      <c r="AV10" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2356,56 +2440,64 @@
         </is>
       </c>
       <c r="AF11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG11" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [0, 2], [1, 1]]</t>
+        </is>
+      </c>
+      <c r="AH11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AG11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH11" s="2" t="inlineStr">
+      <c r="AI11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ11" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AI11" s="2" t="inlineStr"/>
-      <c r="AJ11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK11" s="2" t="inlineStr"/>
+      <c r="AL11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM11" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AN11" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AO11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP11" s="2" t="n">
-        <v>1</v>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AQ11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS11" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AR11" s="2" t="n">
+      <c r="AT11" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AS11" s="2" t="inlineStr">
+      <c r="AU11" s="2" t="inlineStr">
         <is>
           <t>dragon lair, cave, mythical den</t>
         </is>
       </c>
-      <c r="AT11" s="2" t="n">
+      <c r="AV11" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2534,56 +2626,64 @@
         </is>
       </c>
       <c r="AF12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG12" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [0, 2], [1, 0], [1, 1], [1, 2]]</t>
+        </is>
+      </c>
+      <c r="AH12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AG12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH12" s="2" t="inlineStr">
+      <c r="AI12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ12" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AI12" s="2" t="inlineStr"/>
-      <c r="AJ12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK12" s="2" t="inlineStr"/>
+      <c r="AL12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AN12" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AO12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP12" s="2" t="n">
+      <c r="AO12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR12" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AQ12" s="2" t="n">
+      <c r="AS12" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="AR12" s="2" t="n">
+      <c r="AT12" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AS12" s="2" t="inlineStr">
+      <c r="AU12" s="2" t="inlineStr">
         <is>
           <t>somersault, tumble, playful roll</t>
         </is>
       </c>
-      <c r="AT12" s="2" t="n">
+      <c r="AV12" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2718,23 +2818,23 @@
       <c r="AF13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AG13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH13" s="2" t="inlineStr">
+      <c r="AG13" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 1], [1, 0], [1, 1]]</t>
+        </is>
+      </c>
+      <c r="AH13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ13" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AI13" s="2" t="inlineStr"/>
-      <c r="AJ13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AK13" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AK13" s="2" t="inlineStr"/>
       <c r="AL13" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -2749,23 +2849,31 @@
         </is>
       </c>
       <c r="AO13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR13" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AQ13" s="2" t="n">
+      <c r="AS13" s="2" t="n">
         <v>45.33333333</v>
       </c>
-      <c r="AR13" s="2" t="n">
+      <c r="AT13" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AS13" s="2" t="inlineStr">
+      <c r="AU13" s="2" t="inlineStr">
         <is>
           <t>ladybug, spotted beetle, garden friend</t>
         </is>
       </c>
-      <c r="AT13" s="2" t="n">
+      <c r="AV13" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2794,7 +2902,7 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2000</v>
+        <v>1750</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>7</v>
@@ -2890,56 +2998,64 @@
         </is>
       </c>
       <c r="AF14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG14" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG14" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [2, 0], [2, 1], [3, 0], [4, 0]]</t>
+        </is>
+      </c>
+      <c r="AH14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI14" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AH14" s="2" t="inlineStr">
+      <c r="AJ14" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AI14" s="2" t="n">
+      <c r="AK14" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AJ14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK14" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AL14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AM14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AN14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP14" s="2" t="n">
-        <v>1</v>
+      <c r="AM14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AQ14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS14" s="2" t="n">
         <v>57.5</v>
       </c>
-      <c r="AR14" s="2" t="n">
+      <c r="AT14" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="AS14" s="2" t="inlineStr">
+      <c r="AU14" s="2" t="inlineStr">
         <is>
           <t>rainbow, colorful arc, after rain</t>
         </is>
       </c>
-      <c r="AT14" s="2" t="n">
+      <c r="AV14" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3066,29 +3182,29 @@
         </is>
       </c>
       <c r="AF15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH15" s="2" t="inlineStr">
-        <is>
-          <t>prickad</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="AG15" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [1, 0], [1, 1], [2, 0], [2, 1]]</t>
+        </is>
+      </c>
+      <c r="AH15" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AI15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AJ15" s="2" t="n">
-        <v>1</v>
+      <c r="AJ15" s="2" t="inlineStr">
+        <is>
+          <t>prickad</t>
+        </is>
       </c>
       <c r="AK15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AL15" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AM15" s="2" t="n">
         <v>1</v>
@@ -3101,21 +3217,29 @@
       <c r="AO15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP15" s="2" t="n">
-        <v>1</v>
+      <c r="AP15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AQ15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS15" s="2" t="n">
         <v>50.4</v>
       </c>
-      <c r="AR15" s="2" t="n">
+      <c r="AT15" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="AS15" s="2" t="inlineStr">
+      <c r="AU15" s="2" t="inlineStr">
         <is>
           <t>treasure chest, golden chest, pirate loot</t>
         </is>
       </c>
-      <c r="AT15" s="2" t="n">
+      <c r="AV15" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3240,56 +3364,64 @@
         </is>
       </c>
       <c r="AF16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG16" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [1, 1], [2, 0], [3, 0], [4, 0]]</t>
+        </is>
+      </c>
+      <c r="AH16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AH16" s="2" t="inlineStr">
+      <c r="AJ16" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AI16" s="2" t="n">
+      <c r="AK16" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AJ16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK16" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AL16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AM16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AN16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP16" s="2" t="n">
-        <v>1</v>
+      <c r="AM16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AQ16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS16" s="2" t="n">
         <v>54.28571429</v>
       </c>
-      <c r="AR16" s="2" t="n">
+      <c r="AT16" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="AS16" s="2" t="inlineStr">
+      <c r="AU16" s="2" t="inlineStr">
         <is>
           <t>wild strawberry patch, secret spot, hidden paradise</t>
         </is>
       </c>
-      <c r="AT16" s="2" t="n">
+      <c r="AV16" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3416,58 +3548,66 @@
         </is>
       </c>
       <c r="AF17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AH17" s="2" t="inlineStr">
+      <c r="AG17" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [1, 0], [1, 1], [2, 0]]</t>
+        </is>
+      </c>
+      <c r="AH17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI17" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ17" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AI17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ17" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AK17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AL17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM17" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AN17" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AO17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP17" s="2" t="n">
+      <c r="AO17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR17" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AQ17" s="2" t="n">
+      <c r="AS17" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="AR17" s="2" t="n">
+      <c r="AT17" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="AS17" s="2" t="inlineStr">
+      <c r="AU17" s="2" t="inlineStr">
         <is>
           <t>star seed, cosmic sprout, celestial growth</t>
         </is>
       </c>
-      <c r="AT17" s="2" t="n">
+      <c r="AV17" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3592,56 +3732,64 @@
         </is>
       </c>
       <c r="AF18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AH18" s="2" t="inlineStr">
+      <c r="AG18" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 1], [1, 1], [2, 0], [2, 1], [3, 1]]</t>
+        </is>
+      </c>
+      <c r="AH18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ18" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AI18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AK18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AL18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AM18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AN18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AN18" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AO18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP18" s="2" t="n">
+      <c r="AP18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR18" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AQ18" s="2" t="n">
+      <c r="AS18" s="2" t="n">
         <v>53.6</v>
       </c>
-      <c r="AR18" s="2" t="n">
+      <c r="AT18" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="AS18" s="2" t="inlineStr">
+      <c r="AU18" s="2" t="inlineStr">
         <is>
           <t>enchanted forest, magical woods, fairy tale grove</t>
         </is>
       </c>
-      <c r="AT18" s="2" t="n">
+      <c r="AV18" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3766,29 +3914,29 @@
         </is>
       </c>
       <c r="AF19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AH19" s="2" t="inlineStr">
+      <c r="AG19" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 1], [0, 3], [1, 0], [1, 1], [1, 2], [1, 3]]</t>
+        </is>
+      </c>
+      <c r="AH19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI19" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ19" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AI19" s="2" t="n">
+      <c r="AK19" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AJ19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AL19" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AM19" s="2" t="n">
         <v>1</v>
@@ -3799,23 +3947,31 @@
         </is>
       </c>
       <c r="AO19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR19" s="2" t="n">
         <v>1.05</v>
       </c>
-      <c r="AQ19" s="2" t="n">
+      <c r="AS19" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="AR19" s="2" t="n">
+      <c r="AT19" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="AS19" s="2" t="inlineStr">
+      <c r="AU19" s="2" t="inlineStr">
         <is>
           <t>coltsfoot flower, early spring bloom, yellow wildflower</t>
         </is>
       </c>
-      <c r="AT19" s="2" t="n">
+      <c r="AV19" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3946,52 +4102,60 @@
       <c r="AF20" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AG20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH20" s="2" t="inlineStr">
+      <c r="AG20" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 1]]</t>
+        </is>
+      </c>
+      <c r="AH20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ20" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AI20" s="2" t="inlineStr"/>
-      <c r="AJ20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK20" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AK20" s="2" t="inlineStr"/>
       <c r="AL20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AN20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ20" s="2" t="n">
+      <c r="AN20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS20" s="2" t="n">
         <v>46.66666667</v>
       </c>
-      <c r="AR20" s="2" t="n">
+      <c r="AT20" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AS20" s="2" t="inlineStr">
+      <c r="AU20" s="2" t="inlineStr">
         <is>
           <t>the pawn, chess piece, opening move</t>
         </is>
       </c>
-      <c r="AT20" s="2" t="n">
+      <c r="AV20" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4120,54 +4284,62 @@
         </is>
       </c>
       <c r="AF21" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG21" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 1], [2, 0], [2, 1]]</t>
+        </is>
+      </c>
+      <c r="AH21" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AG21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH21" s="2" t="inlineStr">
+      <c r="AI21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ21" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AI21" s="2" t="inlineStr"/>
-      <c r="AJ21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK21" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AK21" s="2" t="inlineStr"/>
       <c r="AL21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AN21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP21" s="2" t="n">
+      <c r="AN21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR21" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AQ21" s="2" t="n">
+      <c r="AS21" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AR21" s="2" t="n">
+      <c r="AT21" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AS21" s="2" t="inlineStr">
+      <c r="AU21" s="2" t="inlineStr">
         <is>
           <t>the queen, chess piece, powerful move</t>
         </is>
       </c>
-      <c r="AT21" s="2" t="n">
+      <c r="AV21" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4296,54 +4468,62 @@
         </is>
       </c>
       <c r="AF22" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG22" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [1, 1], [2, 0], [2, 1], [2, 2]]</t>
+        </is>
+      </c>
+      <c r="AH22" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AG22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH22" s="2" t="inlineStr">
+      <c r="AI22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ22" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AI22" s="2" t="inlineStr"/>
-      <c r="AJ22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK22" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AK22" s="2" t="inlineStr"/>
       <c r="AL22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AM22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AN22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP22" s="2" t="n">
+      <c r="AN22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR22" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AQ22" s="2" t="n">
+      <c r="AS22" s="2" t="n">
         <v>41.71428571</v>
       </c>
-      <c r="AR22" s="2" t="n">
+      <c r="AT22" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AS22" s="2" t="inlineStr">
+      <c r="AU22" s="2" t="inlineStr">
         <is>
           <t>the gambit, chess sacrifice, strategic opening</t>
         </is>
       </c>
-      <c r="AT22" s="2" t="n">
+      <c r="AV22" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4470,56 +4650,64 @@
         </is>
       </c>
       <c r="AF23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG23" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG23" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [1, 0], [1, 1], [2, 0], [2, 1], [3, 0], [4, 0]]</t>
+        </is>
+      </c>
+      <c r="AH23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AH23" s="2" t="inlineStr">
+      <c r="AJ23" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AI23" s="2" t="n">
+      <c r="AK23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AJ23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK23" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AL23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AN23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP23" s="2" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AM23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AQ23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS23" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="AR23" s="2" t="n">
+      <c r="AT23" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="AS23" s="2" t="inlineStr">
+      <c r="AU23" s="2" t="inlineStr">
         <is>
           <t>the king, chess piece, royal protection</t>
         </is>
       </c>
-      <c r="AT23" s="2" t="n">
+      <c r="AV23" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4648,56 +4836,64 @@
         </is>
       </c>
       <c r="AF24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG24" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG24" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [1, 0], [1, 1], [2, 0], [2, 1]]</t>
+        </is>
+      </c>
+      <c r="AH24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI24" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AH24" s="2" t="inlineStr">
+      <c r="AJ24" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AI24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ24" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AK24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AN24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP24" s="2" t="n">
+      <c r="AN24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR24" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AQ24" s="2" t="n">
+      <c r="AS24" s="2" t="n">
         <v>48.8</v>
       </c>
-      <c r="AR24" s="2" t="n">
+      <c r="AT24" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="AS24" s="2" t="inlineStr">
+      <c r="AU24" s="2" t="inlineStr">
         <is>
           <t>the bishop, chess piece, diagonal move</t>
         </is>
       </c>
-      <c r="AT24" s="2" t="n">
+      <c r="AV24" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4826,58 +5022,66 @@
         </is>
       </c>
       <c r="AF25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH25" s="2" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="AG25" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [1, 0], [1, 1], [2, 1]]</t>
+        </is>
+      </c>
+      <c r="AH25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ25" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AI25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AK25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL25" s="2" t="n">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="AL25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AM25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AN25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP25" s="2" t="n">
+      <c r="AN25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR25" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AQ25" s="2" t="n">
+      <c r="AS25" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="AR25" s="2" t="n">
+      <c r="AT25" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="AS25" s="2" t="inlineStr">
+      <c r="AU25" s="2" t="inlineStr">
         <is>
           <t>the countermove, chess response, defensive play</t>
         </is>
       </c>
-      <c r="AT25" s="2" t="n">
+      <c r="AV25" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5006,22 +5210,24 @@
         </is>
       </c>
       <c r="AF26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH26" s="2" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="AG26" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [1, 0]]</t>
+        </is>
+      </c>
+      <c r="AH26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ26" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AI26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ26" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AK26" s="2" t="n">
         <v>1</v>
       </c>
@@ -5031,29 +5237,35 @@
       <c r="AM26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AN26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AN26" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AO26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP26" s="2" t="n">
-        <v>1</v>
+      <c r="AP26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AQ26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS26" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="AR26" s="2" t="n">
+      <c r="AT26" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="AS26" s="2" t="inlineStr">
+      <c r="AU26" s="2" t="inlineStr">
         <is>
           <t>castling, chess maneuver, king safety</t>
         </is>
       </c>
-      <c r="AT26" s="2" t="n">
+      <c r="AV26" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5180,56 +5392,64 @@
         </is>
       </c>
       <c r="AF27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG27" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AH27" s="2" t="inlineStr">
+      <c r="AG27" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [2, 0], [2, 1], [3, 0], [4, 0], [4, 1]]</t>
+        </is>
+      </c>
+      <c r="AH27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI27" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ27" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AI27" s="2" t="n">
+      <c r="AK27" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AJ27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK27" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AL27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AN27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP27" s="2" t="n">
+      <c r="AN27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR27" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AQ27" s="2" t="n">
+      <c r="AS27" s="2" t="n">
         <v>55.5</v>
       </c>
-      <c r="AR27" s="2" t="n">
+      <c r="AT27" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="AS27" s="2" t="inlineStr">
+      <c r="AU27" s="2" t="inlineStr">
         <is>
           <t>the knight, chess piece, L-shaped move</t>
         </is>
       </c>
-      <c r="AT27" s="2" t="n">
+      <c r="AV27" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5356,54 +5576,62 @@
         </is>
       </c>
       <c r="AF28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG28" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AH28" s="2" t="inlineStr">
+      <c r="AG28" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 1], [2, 1], [3, 1], [4, 0], [4, 1]]</t>
+        </is>
+      </c>
+      <c r="AH28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI28" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ28" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AI28" s="2" t="n">
+      <c r="AK28" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AJ28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK28" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AL28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AN28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AN28" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AO28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP28" s="2" t="n">
+      <c r="AP28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR28" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AQ28" s="2" t="n">
+      <c r="AS28" s="2" t="n">
         <v>54.85714286</v>
       </c>
-      <c r="AR28" s="2" t="n">
+      <c r="AT28" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="AS28" s="2" t="inlineStr">
+      <c r="AU28" s="2" t="inlineStr">
         <is>
           <t>the rook, chess piece, straight power</t>
         </is>
       </c>
-      <c r="AT28" s="2" t="n">
+      <c r="AV28" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5530,54 +5758,62 @@
         </is>
       </c>
       <c r="AF29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG29" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [1, 0], [1, 1], [2, 0]]</t>
+        </is>
+      </c>
+      <c r="AH29" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AG29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH29" s="2" t="inlineStr">
+      <c r="AI29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ29" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AI29" s="2" t="inlineStr"/>
-      <c r="AJ29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AK29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL29" s="2" t="n">
-        <v>1</v>
+      <c r="AK29" s="2" t="inlineStr"/>
+      <c r="AL29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AM29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AN29" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AO29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AP29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AQ29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS29" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AR29" s="2" t="n">
+      <c r="AT29" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AS29" s="2" t="inlineStr">
+      <c r="AU29" s="2" t="inlineStr">
         <is>
           <t>galaxy, spiral nebula, cosmic swirl</t>
         </is>
       </c>
-      <c r="AT29" s="2" t="n">
+      <c r="AV29" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5704,54 +5940,62 @@
         </is>
       </c>
       <c r="AF30" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG30" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 2], [1, 0], [1, 1], [1, 2], [2, 0], [2, 1]]</t>
+        </is>
+      </c>
+      <c r="AH30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AG30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH30" s="2" t="inlineStr">
+      <c r="AI30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ30" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AI30" s="2" t="inlineStr"/>
-      <c r="AJ30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AK30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL30" s="2" t="n">
-        <v>1</v>
+      <c r="AK30" s="2" t="inlineStr"/>
+      <c r="AL30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AM30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AN30" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AO30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR30" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AQ30" s="2" t="n">
+      <c r="AS30" s="2" t="n">
         <v>43.33333333</v>
       </c>
-      <c r="AR30" s="2" t="n">
+      <c r="AT30" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AS30" s="2" t="inlineStr">
+      <c r="AU30" s="2" t="inlineStr">
         <is>
           <t>lighthouse, beacon tower, guiding light</t>
         </is>
       </c>
-      <c r="AT30" s="2" t="n">
+      <c r="AV30" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5878,54 +6122,62 @@
         </is>
       </c>
       <c r="AF31" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG31" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [1, 1], [1, 2], [2, 0], [2, 1], [2, 2]]</t>
+        </is>
+      </c>
+      <c r="AH31" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AG31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH31" s="2" t="inlineStr">
+      <c r="AI31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ31" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AI31" s="2" t="inlineStr"/>
-      <c r="AJ31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AK31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL31" s="2" t="n">
-        <v>2</v>
+      <c r="AK31" s="2" t="inlineStr"/>
+      <c r="AL31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AM31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AN31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AN31" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AO31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP31" s="2" t="n">
+      <c r="AP31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR31" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AQ31" s="2" t="n">
+      <c r="AS31" s="2" t="n">
         <v>41.5</v>
       </c>
-      <c r="AR31" s="2" t="n">
+      <c r="AT31" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AS31" s="2" t="inlineStr">
+      <c r="AU31" s="2" t="inlineStr">
         <is>
           <t>bastion, fortified tower, stronghold</t>
         </is>
       </c>
-      <c r="AT31" s="2" t="n">
+      <c r="AV31" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6054,56 +6306,64 @@
         </is>
       </c>
       <c r="AF32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG32" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG32" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [1, 1], [2, 0]]</t>
+        </is>
+      </c>
+      <c r="AH32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AH32" s="2" t="inlineStr">
+      <c r="AJ32" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AI32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AK32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AL32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AM32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AN32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AN32" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AO32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP32" s="2" t="n">
-        <v>1</v>
+      <c r="AP32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AQ32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS32" s="2" t="n">
         <v>48.8</v>
       </c>
-      <c r="AR32" s="2" t="n">
+      <c r="AT32" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="AS32" s="2" t="inlineStr">
+      <c r="AU32" s="2" t="inlineStr">
         <is>
           <t>nebula, cosmic cloud, star nursery</t>
         </is>
       </c>
-      <c r="AT32" s="2" t="n">
+      <c r="AV32" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6234,56 +6494,64 @@
         </is>
       </c>
       <c r="AF33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG33" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG33" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [0, 2], [0, 3], [1, 0], [1, 1], [2, 0]]</t>
+        </is>
+      </c>
+      <c r="AH33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI33" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AH33" s="2" t="inlineStr">
+      <c r="AJ33" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AI33" s="2" t="n">
+      <c r="AK33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AJ33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AK33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL33" s="2" t="n">
-        <v>1</v>
+      <c r="AL33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AM33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AN33" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AO33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR33" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AQ33" s="2" t="n">
+      <c r="AS33" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="AR33" s="2" t="n">
+      <c r="AT33" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="AS33" s="2" t="inlineStr">
+      <c r="AU33" s="2" t="inlineStr">
         <is>
           <t>quadrant, navigation instrument, star chart</t>
         </is>
       </c>
-      <c r="AT33" s="2" t="n">
+      <c r="AV33" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6410,54 +6678,62 @@
         </is>
       </c>
       <c r="AF34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG34" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG34" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 1], [0, 2], [0, 3], [1, 0], [1, 1], [1, 3], [2, 0]]</t>
+        </is>
+      </c>
+      <c r="AH34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI34" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AH34" s="2" t="inlineStr">
+      <c r="AJ34" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AI34" s="2" t="n">
+      <c r="AK34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AJ34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK34" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AL34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AM34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AN34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AN34" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AO34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP34" s="2" t="n">
+      <c r="AP34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR34" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AQ34" s="2" t="n">
+      <c r="AS34" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="AR34" s="2" t="n">
+      <c r="AT34" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="AS34" s="2" t="inlineStr">
+      <c r="AU34" s="2" t="inlineStr">
         <is>
           <t>comet path, orbital trail, stellar trajectory</t>
         </is>
       </c>
-      <c r="AT34" s="2" t="n">
+      <c r="AV34" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6584,56 +6860,64 @@
         </is>
       </c>
       <c r="AF35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG35" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AH35" s="2" t="inlineStr">
+      <c r="AG35" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [0, 2], [0, 3], [1, 0], [1, 3], [2, 0], [2, 3]]</t>
+        </is>
+      </c>
+      <c r="AH35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI35" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ35" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AI35" s="2" t="n">
+      <c r="AK35" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AJ35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AK35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL35" s="2" t="n">
-        <v>1</v>
+      <c r="AL35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AM35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AN35" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AO35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AP35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AQ35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS35" s="2" t="n">
         <v>58.5</v>
       </c>
-      <c r="AR35" s="2" t="n">
+      <c r="AT35" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="AS35" s="2" t="inlineStr">
+      <c r="AU35" s="2" t="inlineStr">
         <is>
           <t>star harbor, celestial port, cosmic dock</t>
         </is>
       </c>
-      <c r="AT35" s="2" t="n">
+      <c r="AV35" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6760,54 +7044,62 @@
         </is>
       </c>
       <c r="AF36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG36" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AH36" s="2" t="inlineStr">
+      <c r="AG36" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 3], [1, 3], [2, 1], [2, 3], [3, 0], [3, 1], [3, 2], [3, 3]]</t>
+        </is>
+      </c>
+      <c r="AH36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI36" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ36" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AI36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ36" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AK36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AM36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AN36" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AO36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR36" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AQ36" s="2" t="n">
+      <c r="AS36" s="2" t="n">
         <v>55.5</v>
       </c>
-      <c r="AR36" s="2" t="n">
+      <c r="AT36" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="AS36" s="2" t="inlineStr">
+      <c r="AU36" s="2" t="inlineStr">
         <is>
           <t>space axis, cosmic alignment, stellar center</t>
         </is>
       </c>
-      <c r="AT36" s="2" t="n">
+      <c r="AV36" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6934,56 +7226,64 @@
         </is>
       </c>
       <c r="AF37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG37" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AH37" s="2" t="inlineStr">
+      <c r="AG37" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 3], [1, 3], [2, 2], [2, 3], [3, 0], [3, 1], [3, 2], [3, 3]]</t>
+        </is>
+      </c>
+      <c r="AH37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI37" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ37" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AI37" s="2" t="n">
+      <c r="AK37" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AJ37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AK37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL37" s="2" t="n">
-        <v>2</v>
+      <c r="AL37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AM37" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AN37" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AO37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR37" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AQ37" s="2" t="n">
+      <c r="AS37" s="2" t="n">
         <v>59.5</v>
       </c>
-      <c r="AR37" s="2" t="n">
+      <c r="AT37" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="AS37" s="2" t="inlineStr">
+      <c r="AU37" s="2" t="inlineStr">
         <is>
           <t>observatory, telescope dome, stargazing</t>
         </is>
       </c>
-      <c r="AT37" s="2" t="n">
+      <c r="AV37" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7118,54 +7418,62 @@
       <c r="AF38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AG38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH38" s="2" t="inlineStr">
+      <c r="AG38" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0]]</t>
+        </is>
+      </c>
+      <c r="AH38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ38" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AI38" s="2" t="inlineStr"/>
-      <c r="AJ38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AK38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AN38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP38" s="2" t="n">
-        <v>1</v>
+      <c r="AK38" s="2" t="inlineStr"/>
+      <c r="AL38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AQ38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS38" s="2" t="n">
         <v>45.33333333</v>
       </c>
-      <c r="AR38" s="2" t="n">
+      <c r="AT38" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AS38" s="2" t="inlineStr">
+      <c r="AU38" s="2" t="inlineStr">
         <is>
           <t>harbor change, port transition, dock shift</t>
         </is>
       </c>
-      <c r="AT38" s="2" t="n">
+      <c r="AV38" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7294,56 +7602,64 @@
         </is>
       </c>
       <c r="AF39" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG39" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 1], [0, 2], [1, 0], [1, 1], [1, 2]]</t>
+        </is>
+      </c>
+      <c r="AH39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AG39" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH39" s="2" t="inlineStr">
+      <c r="AI39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ39" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AI39" s="2" t="inlineStr"/>
-      <c r="AJ39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AK39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL39" s="2" t="n">
-        <v>2</v>
+      <c r="AK39" s="2" t="inlineStr"/>
+      <c r="AL39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AM39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AN39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP39" s="2" t="n">
+      <c r="AN39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR39" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AQ39" s="2" t="n">
+      <c r="AS39" s="2" t="n">
         <v>42.4</v>
       </c>
-      <c r="AR39" s="2" t="n">
+      <c r="AT39" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AS39" s="2" t="inlineStr">
+      <c r="AU39" s="2" t="inlineStr">
         <is>
           <t>birdsong, avian melody, morning chorus</t>
         </is>
       </c>
-      <c r="AT39" s="2" t="n">
+      <c r="AV39" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7472,58 +7788,66 @@
         </is>
       </c>
       <c r="AF40" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG40" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [1, 1], [2, 0], [2, 1]]</t>
+        </is>
+      </c>
+      <c r="AH40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AG40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH40" s="2" t="inlineStr">
+      <c r="AI40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ40" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AI40" s="2" t="n">
+      <c r="AK40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AJ40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AK40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AN40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP40" s="2" t="n">
+      <c r="AL40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR40" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AQ40" s="2" t="n">
+      <c r="AS40" s="2" t="n">
         <v>47.33333333</v>
       </c>
-      <c r="AR40" s="2" t="n">
+      <c r="AT40" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="AS40" s="2" t="inlineStr">
+      <c r="AU40" s="2" t="inlineStr">
         <is>
           <t>mountain slope, hillside, rocky incline</t>
         </is>
       </c>
-      <c r="AT40" s="2" t="n">
+      <c r="AV40" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7654,58 +7978,66 @@
         </is>
       </c>
       <c r="AF41" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH41" s="2" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="AG41" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0]]</t>
+        </is>
+      </c>
+      <c r="AH41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ41" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AI41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AK41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AL41" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN41" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AO41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP41" s="2" t="n">
-        <v>1</v>
+      <c r="AP41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AQ41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS41" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="AR41" s="2" t="n">
+      <c r="AT41" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="AS41" s="2" t="inlineStr">
+      <c r="AU41" s="2" t="inlineStr">
         <is>
           <t>rose grove, flowering garden, romantic park</t>
         </is>
       </c>
-      <c r="AT41" s="2" t="n">
+      <c r="AV41" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7832,58 +8164,66 @@
         </is>
       </c>
       <c r="AF42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG42" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG42" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [0, 2], [1, 1], [1, 2]]</t>
+        </is>
+      </c>
+      <c r="AH42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AH42" s="2" t="inlineStr">
+      <c r="AJ42" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AI42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AK42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AL42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AN42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP42" s="2" t="n">
+      <c r="AL42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR42" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AQ42" s="2" t="n">
+      <c r="AS42" s="2" t="n">
         <v>49.6</v>
       </c>
-      <c r="AR42" s="2" t="n">
+      <c r="AT42" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="AS42" s="2" t="inlineStr">
+      <c r="AU42" s="2" t="inlineStr">
         <is>
           <t>leaf meadow, deciduous clearing, green pasture</t>
         </is>
       </c>
-      <c r="AT42" s="2" t="n">
+      <c r="AV42" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8010,56 +8350,64 @@
         </is>
       </c>
       <c r="AF43" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG43" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG43" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [1, 1], [2, 0], [3, 0]]</t>
+        </is>
+      </c>
+      <c r="AH43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI43" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AH43" s="2" t="inlineStr">
+      <c r="AJ43" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AI43" s="2" t="n">
+      <c r="AK43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AJ43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK43" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AL43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AM43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AN43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP43" s="2" t="n">
+      <c r="AM43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR43" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AQ43" s="2" t="n">
+      <c r="AS43" s="2" t="n">
         <v>51.33333333</v>
       </c>
-      <c r="AR43" s="2" t="n">
+      <c r="AT43" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="AS43" s="2" t="inlineStr">
+      <c r="AU43" s="2" t="inlineStr">
         <is>
           <t>mill hill, grinding slope, water mill</t>
         </is>
       </c>
-      <c r="AT43" s="2" t="n">
+      <c r="AV43" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8190,56 +8538,64 @@
         </is>
       </c>
       <c r="AF44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH44" s="2" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="AG44" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 1]]</t>
+        </is>
+      </c>
+      <c r="AH44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ44" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AI44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AK44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AL44" s="2" t="n">
-        <v>1</v>
+      <c r="AL44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AM44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AN44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AN44" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AO44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP44" s="2" t="n">
-        <v>1</v>
+      <c r="AP44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AQ44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS44" s="2" t="n">
         <v>50.66666667</v>
       </c>
-      <c r="AR44" s="2" t="n">
+      <c r="AT44" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="AS44" s="2" t="inlineStr">
+      <c r="AU44" s="2" t="inlineStr">
         <is>
           <t>river bank, stream edge, waterside</t>
         </is>
       </c>
-      <c r="AT44" s="2" t="n">
+      <c r="AV44" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8364,56 +8720,64 @@
         </is>
       </c>
       <c r="AF45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG45" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AH45" s="2" t="inlineStr">
+      <c r="AG45" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [2, 0], [3, 0], [3, 1], [3, 2], [3, 3]]</t>
+        </is>
+      </c>
+      <c r="AH45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI45" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ45" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AI45" s="2" t="n">
+      <c r="AK45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AJ45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK45" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AL45" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AN45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR45" s="2" t="n">
         <v>1.05</v>
       </c>
-      <c r="AQ45" s="2" t="n">
+      <c r="AS45" s="2" t="n">
         <v>56.5</v>
       </c>
-      <c r="AR45" s="2" t="n">
+      <c r="AT45" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="AS45" s="2" t="inlineStr">
+      <c r="AU45" s="2" t="inlineStr">
         <is>
           <t>stone edge, rock ridge, granite brow</t>
         </is>
       </c>
-      <c r="AT45" s="2" t="n">
+      <c r="AV45" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8542,56 +8906,64 @@
         </is>
       </c>
       <c r="AF46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG46" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AH46" s="2" t="inlineStr">
+      <c r="AG46" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 3], [1, 1], [1, 3], [2, 0], [2, 1], [2, 2], [2, 3]]</t>
+        </is>
+      </c>
+      <c r="AH46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI46" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ46" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AI46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AK46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL46" s="2" t="n">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="AL46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AM46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AN46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AN46" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AO46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP46" s="2" t="n">
+      <c r="AP46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR46" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AQ46" s="2" t="n">
+      <c r="AS46" s="2" t="n">
         <v>53.71428571</v>
       </c>
-      <c r="AR46" s="2" t="n">
+      <c r="AT46" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="AS46" s="2" t="inlineStr">
+      <c r="AU46" s="2" t="inlineStr">
         <is>
           <t>lake glimmer, water sparkle, shimmering shore</t>
         </is>
       </c>
-      <c r="AT46" s="2" t="n">
+      <c r="AV46" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11918,7 +12290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -12622,12 +12994,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Förekomst</t>
+          <t>Antal rutor</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Förekomst</t>
+          <t>F_rutor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -12637,19 +13009,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ej tryckt — speldata</t>
+          <t>Ej tryckt — brickans storlek; en ruta = 250 kvm (= BTA / 250)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Formfaktor</t>
+          <t>Form (rutor)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Formfaktor</t>
+          <t>F_form</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -12659,19 +13031,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ej tryckt — styr brickans form (1–8)</t>
+          <t>Ej tryckt — brickans form som [rad, kolumn] per ruta (från brickorna)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Linjetyp</t>
+          <t>Förekomst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>linjetyp</t>
+          <t>Förekomst</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -12681,19 +13053,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ej tryckt — ramens linjestil</t>
+          <t>Ej tryckt — speldata</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Antal krav</t>
+          <t>Formfaktor</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Antal krav</t>
+          <t>Formfaktor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -12703,19 +13075,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ej tryckt</t>
+          <t>Ej tryckt — styr brickans form (1–8)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>Linjetyp</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>linjetyp</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -12725,19 +13097,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ej tryckt — kompetens</t>
+          <t>Ej tryckt — ramens linjestil</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KOM</t>
+          <t>Antal krav</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>KOM</t>
+          <t>Antal krav</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -12747,19 +13119,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ej tryckt — kompetens</t>
+          <t>Ej tryckt</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -12776,12 +13148,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NOG</t>
+          <t>KOM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NOG</t>
+          <t>KOM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -12798,12 +13170,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>INN</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>INN</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -12820,12 +13192,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ABM</t>
+          <t>NOG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ABM</t>
+          <t>NOG</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -12842,12 +13214,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Skalfaktor</t>
+          <t>INN</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Skalfaktor</t>
+          <t>INN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -12857,19 +13229,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ej tryckt</t>
+          <t>Ej tryckt — kompetens</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Intäkt/kvm nu</t>
+          <t>ABM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>intäkt/kvm nu</t>
+          <t>ABM</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -12879,19 +13251,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ej tryckt — beräkningsunderlag</t>
+          <t>Ej tryckt — kompetens</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Förslag intäkt</t>
+          <t>Skalfaktor</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>förslag intäkt</t>
+          <t>Skalfaktor</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -12901,19 +13273,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ej tryckt — beräkningsunderlag</t>
+          <t>Ej tryckt</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bildprompt (en)</t>
+          <t>Intäkt/kvm nu</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>namn_en</t>
+          <t>intäkt/kvm nu</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -12923,27 +13295,71 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ej tryckt — underlag för bildgenerering</t>
+          <t>Ej tryckt — beräkningsunderlag</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>Förslag intäkt</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>förslag intäkt</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Ej tryckt — beräkningsunderlag</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Bildprompt (en)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>namn_en</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Ej tryckt — underlag för bildgenerering</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>Antal exemplar</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Nej</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Antal tryckta kort (utskrift_config: 1)</t>
         </is>
@@ -12960,7 +13376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13102,22 +13518,46 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Omtryck</t>
+          <t>Omtryck BTA</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Marknadsvärde, energiklass, driftnetto (nu efter ränta, per år), räntekostnad och lån för förvaltningsbara typer kommer från data/forvaltning_2-1/F2-1_projektkort.csv — de tryckta värdena finns kvar i arv/ och i tryckfilens text.</t>
+          <t>Förskolan Regnbågen: BTA 2000 → 1750, så att kortet stämmer med brickans form (7 rutor).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Former</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Brickornas former från data/shapes.json; kontroll: rutor × 250 = BTA för alla 45.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Omtryck</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Marknadsvärde, energiklass, driftnetto (nu efter ränta, per år), räntekostnad och lån för förvaltningsbara typer kommer från data/forvaltning_2-1/F2-1_projektkort.csv — de tryckta värdena finns kvar i arv/ och i tryckfilens text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Byggd med</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>verktyg/bygg_pu_projekt_excel.py</t>
         </is>

--- a/kortdata/PU_projekt.xlsx
+++ b/kortdata/PU_projekt.xlsx
@@ -7318,7 +7318,7 @@
         <v>2</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I38" s="2" t="n">
         <v>1</v>
@@ -7508,7 +7508,7 @@
         <v>3</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="I39" s="2" t="n">
         <v>1</v>
@@ -7694,7 +7694,7 @@
         <v>4</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I40" s="2" t="n">
         <v>1</v>
@@ -7882,7 +7882,7 @@
         <v>2</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I41" s="2" t="n">
         <v>1</v>
@@ -8072,7 +8072,7 @@
         <v>4</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I42" s="2" t="n">
         <v>1</v>
@@ -8258,7 +8258,7 @@
         <v>5</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I43" s="2" t="n">
         <v>1</v>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>Balanserad</t>
+          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr"/>
@@ -8442,7 +8442,7 @@
         <v>2</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I44" s="2" t="n">
         <v>2</v>
@@ -8630,7 +8630,7 @@
         <v>7</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="I45" s="2" t="n">
         <v>2</v>
@@ -8812,7 +8812,7 @@
         <v>6</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I46" s="2" t="n">
         <v>2</v>
@@ -8852,7 +8852,7 @@
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>Balanserad</t>
+          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
@@ -13376,7 +13376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13530,34 +13530,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Former</t>
+          <t>Omtryck anskaffning</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Brickornas former från data/shapes.json; kontroll: rutor × 250 = BTA för alla 45.</t>
+          <t>Hyresrätter: anskaffningen sänkt cirka 5 % (tryggt val ska kosta lite i Projektutvecklingen).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Omtryck</t>
+          <t>Former</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Marknadsvärde, energiklass, driftnetto (nu efter ränta, per år), räntekostnad och lån för förvaltningsbara typer kommer från data/forvaltning_2-1/F2-1_projektkort.csv — de tryckta värdena finns kvar i arv/ och i tryckfilens text.</t>
+          <t>Brickornas former från data/shapes.json; kontroll: rutor × 250 = BTA för alla 45.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Omtryck</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Marknadsvärde, energiklass, driftnetto (nu efter ränta, per år), räntekostnad och lån för förvaltningsbara typer kommer från data/forvaltning_2-1/F2-1_projektkort.csv — de tryckta värdena finns kvar i arv/ och i tryckfilens text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Byggd med</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>verktyg/bygg_pu_projekt_excel.py</t>
         </is>

--- a/kortdata/PU_projekt.xlsx
+++ b/kortdata/PU_projekt.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV46"/>
+  <dimension ref="A1:AX46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -483,6 +483,8 @@
     <col width="14" customWidth="1" min="46" max="46"/>
     <col width="14" customWidth="1" min="47" max="47"/>
     <col width="14" customWidth="1" min="48" max="48"/>
+    <col width="14" customWidth="1" min="49" max="49"/>
+    <col width="14" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -598,130 +600,140 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>MV-faktor</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Motvikt</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>Nivåkrav Mark</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Nivåkrav Husunderbyggnad</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Nivåkrav Stomme</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Nivåkrav Yttertak</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Nivåkrav Fasader</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Nivåkrav Stomkomplettering</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Nivåkrav Ytskikt</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Nivåkrav Installationer</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Nivåkrav Gemensamma arbeten</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Antal rutor</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Form (rutor)</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Förekomst</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Formfaktor</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Linjetyp</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Antal krav</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>STA</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>KOM</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>SAM</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>NOG</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>INN</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>ABM</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Skalfaktor</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Intäkt/kvm nu</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Förslag intäkt</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Bildprompt (en)</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Antal exemplar</t>
         </is>
@@ -798,16 +810,8 @@
       <c r="T2" s="2" t="inlineStr"/>
       <c r="U2" s="2" t="inlineStr"/>
       <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="W2" s="2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -843,41 +847,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AF2" s="2" t="n">
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AG2" s="2" t="inlineStr">
+      <c r="AI2" s="2" t="inlineStr">
         <is>
           <t>[[0, 0], [1, 0], [1, 1], [1, 2]]</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="n">
+      <c r="AJ2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AI2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ2" s="2" t="inlineStr">
+      <c r="AK2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM2" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="AO2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP2" s="2" t="inlineStr">
         <is>
@@ -887,19 +893,27 @@
       <c r="AQ2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AR2" s="2" t="inlineStr"/>
+      <c r="AR2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AS2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT2" s="2" t="inlineStr"/>
+      <c r="AU2" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="AT2" s="2" t="n">
+      <c r="AV2" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AU2" s="2" t="inlineStr">
+      <c r="AW2" s="2" t="inlineStr">
         <is>
           <t>fire, burning flames, ember glow</t>
         </is>
       </c>
-      <c r="AV2" s="2" t="n">
+      <c r="AX2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -974,16 +988,8 @@
       <c r="T3" s="2" t="inlineStr"/>
       <c r="U3" s="2" t="inlineStr"/>
       <c r="V3" s="2" t="inlineStr"/>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr"/>
       <c r="Y3" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -1019,63 +1025,73 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AF3" s="2" t="n">
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH3" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AG3" s="2" t="inlineStr">
+      <c r="AI3" s="2" t="inlineStr">
         <is>
           <t>[[0, 0], [1, 0], [1, 1], [2, 0], [2, 1], [3, 1]]</t>
         </is>
       </c>
-      <c r="AH3" s="2" t="n">
+      <c r="AJ3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AI3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ3" s="2" t="inlineStr">
+      <c r="AK3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL3" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AQ3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR3" s="2" t="inlineStr"/>
+      <c r="AM3" s="2" t="inlineStr"/>
+      <c r="AN3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AS3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT3" s="2" t="inlineStr"/>
+      <c r="AU3" s="2" t="n">
         <v>40.66666667</v>
       </c>
-      <c r="AT3" s="2" t="n">
+      <c r="AV3" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AU3" s="2" t="inlineStr">
+      <c r="AW3" s="2" t="inlineStr">
         <is>
           <t>forest glade, clearing, sunlight through trees</t>
         </is>
       </c>
-      <c r="AV3" s="2" t="n">
+      <c r="AX3" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1150,16 +1166,8 @@
       <c r="T4" s="2" t="inlineStr"/>
       <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" s="2" t="inlineStr"/>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr"/>
       <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -1195,41 +1203,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AF4" s="2" t="n">
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AG4" s="2" t="inlineStr">
+      <c r="AI4" s="2" t="inlineStr">
         <is>
           <t>[[0, 0], [0, 1], [1, 0], [1, 1], [2, 0], [2, 1], [3, 0], [3, 1]]</t>
         </is>
       </c>
-      <c r="AH4" s="2" t="n">
+      <c r="AJ4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AI4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ4" s="2" t="inlineStr">
+      <c r="AK4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL4" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM4" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="AO4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP4" s="2" t="inlineStr">
         <is>
@@ -1239,19 +1249,27 @@
       <c r="AQ4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AR4" s="2" t="inlineStr"/>
+      <c r="AR4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AS4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT4" s="2" t="inlineStr"/>
+      <c r="AU4" s="2" t="n">
         <v>39.5</v>
       </c>
-      <c r="AT4" s="2" t="n">
+      <c r="AV4" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AU4" s="2" t="inlineStr">
+      <c r="AW4" s="2" t="inlineStr">
         <is>
           <t>wide horizon, distant skyline, open sky</t>
         </is>
       </c>
-      <c r="AV4" s="2" t="n">
+      <c r="AX4" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1326,108 +1344,110 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr"/>
       <c r="V5" s="2" t="inlineStr"/>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr"/>
       <c r="Y5" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="inlineStr">
+        <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AE5" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF5" s="2" t="n">
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH5" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AG5" s="2" t="inlineStr">
+      <c r="AI5" s="2" t="inlineStr">
         <is>
           <t>[[0, 0], [0, 1], [1, 0], [1, 1], [2, 0], [2, 1]]</t>
         </is>
       </c>
-      <c r="AH5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI5" s="2" t="n">
+      <c r="AJ5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AJ5" s="2" t="inlineStr">
+      <c r="AL5" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AK5" s="2" t="n">
+      <c r="AM5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AL5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN5" s="2" t="n">
-        <v>1</v>
+      <c r="AN5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AO5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AP5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AQ5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AR5" s="2" t="inlineStr"/>
+      <c r="AR5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AS5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" s="2" t="inlineStr"/>
+      <c r="AU5" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="AT5" s="2" t="n">
+      <c r="AV5" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="AU5" s="2" t="inlineStr">
+      <c r="AW5" s="2" t="inlineStr">
         <is>
           <t>rocky cliff, stone crag, rugged outcrop</t>
         </is>
       </c>
-      <c r="AV5" s="2" t="n">
+      <c r="AX5" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1500,110 +1520,112 @@
       <c r="T6" s="2" t="inlineStr"/>
       <c r="U6" s="2" t="inlineStr"/>
       <c r="V6" s="2" t="inlineStr"/>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X6" s="2" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr">
+      <c r="AF6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG6" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="AF6" s="2" t="n">
+      <c r="AH6" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AG6" s="2" t="inlineStr">
+      <c r="AI6" s="2" t="inlineStr">
         <is>
           <t>[[0, 0], [0, 1], [1, 0], [2, 0], [3, 0], [4, 0], [4, 1]]</t>
         </is>
       </c>
-      <c r="AH6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI6" s="2" t="n">
+      <c r="AJ6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AJ6" s="2" t="inlineStr">
+      <c r="AL6" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AK6" s="2" t="n">
+      <c r="AM6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AL6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN6" s="2" t="n">
-        <v>1</v>
+      <c r="AN6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AO6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AQ6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AR6" s="2" t="inlineStr"/>
-      <c r="AS6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AT6" s="2" t="inlineStr"/>
+      <c r="AU6" s="2" t="n">
         <v>53.14285714</v>
       </c>
-      <c r="AT6" s="2" t="n">
+      <c r="AV6" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="AU6" s="2" t="inlineStr">
+      <c r="AW6" s="2" t="inlineStr">
         <is>
           <t>golden grain, wheat sheaf, harvest field</t>
         </is>
       </c>
-      <c r="AV6" s="2" t="n">
+      <c r="AX6" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1678,110 +1700,112 @@
       <c r="T7" s="2" t="inlineStr"/>
       <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" s="2" t="inlineStr"/>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr"/>
       <c r="Y7" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="Z7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA7" s="2" t="inlineStr">
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="AE7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF7" s="2" t="n">
+      <c r="AG7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AG7" s="2" t="inlineStr">
+      <c r="AI7" s="2" t="inlineStr">
         <is>
           <t>[[0, 0], [1, 0], [1, 1], [2, 0], [2, 1]]</t>
         </is>
       </c>
-      <c r="AH7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI7" s="2" t="n">
+      <c r="AJ7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AJ7" s="2" t="inlineStr">
+      <c r="AL7" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AK7" s="2" t="n">
+      <c r="AM7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AL7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AN7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AP7" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AQ7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR7" s="2" t="inlineStr"/>
+      <c r="AQ7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AS7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" s="2" t="inlineStr"/>
+      <c r="AU7" s="2" t="n">
         <v>52.8</v>
       </c>
-      <c r="AT7" s="2" t="n">
+      <c r="AV7" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="AU7" s="2" t="inlineStr">
+      <c r="AW7" s="2" t="inlineStr">
         <is>
           <t>sunflower, golden petals, summer bloom</t>
         </is>
       </c>
-      <c r="AV7" s="2" t="n">
+      <c r="AX7" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1856,16 +1880,8 @@
       <c r="T8" s="2" t="inlineStr"/>
       <c r="U8" s="2" t="inlineStr"/>
       <c r="V8" s="2" t="inlineStr"/>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr"/>
       <c r="Y8" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -1873,19 +1889,19 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -1893,43 +1909,45 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AE8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF8" s="2" t="n">
+      <c r="AG8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AG8" s="2" t="inlineStr">
+      <c r="AI8" s="2" t="inlineStr">
         <is>
           <t>[[0, 0], [0, 1], [1, 1], [2, 1]]</t>
         </is>
       </c>
-      <c r="AH8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI8" s="2" t="n">
+      <c r="AJ8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AJ8" s="2" t="inlineStr">
+      <c r="AL8" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AK8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AM8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN8" s="2" t="inlineStr">
         <is>
@@ -1937,7 +1955,7 @@
         </is>
       </c>
       <c r="AO8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP8" s="2" t="inlineStr">
         <is>
@@ -1945,21 +1963,29 @@
         </is>
       </c>
       <c r="AQ8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR8" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AR8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AS8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT8" s="2" t="inlineStr"/>
+      <c r="AU8" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="AT8" s="2" t="n">
+      <c r="AV8" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="AU8" s="2" t="inlineStr">
+      <c r="AW8" s="2" t="inlineStr">
         <is>
           <t>reflection, mirror lake, still water</t>
         </is>
       </c>
-      <c r="AV8" s="2" t="n">
+      <c r="AX8" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2034,16 +2060,8 @@
       <c r="T9" s="2" t="inlineStr"/>
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr"/>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr"/>
       <c r="Y9" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -2056,19 +2074,19 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -2076,68 +2094,78 @@
       </c>
       <c r="AE9" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG9" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AF9" s="2" t="n">
+      <c r="AH9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AG9" s="2" t="inlineStr">
+      <c r="AI9" s="2" t="inlineStr">
         <is>
           <t>[[0, 0], [0, 1], [0, 2]]</t>
         </is>
       </c>
-      <c r="AH9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ9" s="2" t="inlineStr">
+      <c r="AJ9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL9" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AK9" s="2" t="n">
+      <c r="AM9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AL9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AQ9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR9" s="2" t="inlineStr"/>
+      <c r="AN9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AS9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT9" s="2" t="inlineStr"/>
+      <c r="AU9" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="AT9" s="2" t="n">
+      <c r="AV9" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="AU9" s="2" t="inlineStr">
+      <c r="AW9" s="2" t="inlineStr">
         <is>
           <t>forest path, winding trail, woodland walk</t>
         </is>
       </c>
-      <c r="AV9" s="2" t="n">
+      <c r="AX9" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2210,86 +2238,80 @@
       <c r="T10" s="2" t="inlineStr"/>
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr"/>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr"/>
       <c r="Y10" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD10" s="2" t="inlineStr">
+      <c r="AE10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF10" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AE10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF10" s="2" t="n">
+      <c r="AG10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AG10" s="2" t="inlineStr">
+      <c r="AI10" s="2" t="inlineStr">
         <is>
           <t>[[0, 0], [0, 1], [0, 2], [0, 3], [1, 2], [1, 3], [2, 3], [3, 3]]</t>
         </is>
       </c>
-      <c r="AH10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI10" s="2" t="n">
+      <c r="AJ10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK10" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AJ10" s="2" t="inlineStr">
+      <c r="AL10" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AK10" s="2" t="n">
+      <c r="AM10" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AL10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AN10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AO10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP10" s="2" t="inlineStr">
         <is>
@@ -2299,19 +2321,27 @@
       <c r="AQ10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AR10" s="2" t="inlineStr"/>
+      <c r="AR10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AS10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT10" s="2" t="inlineStr"/>
+      <c r="AU10" s="2" t="n">
         <v>59.5</v>
       </c>
-      <c r="AT10" s="2" t="n">
+      <c r="AV10" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="AU10" s="2" t="inlineStr">
+      <c r="AW10" s="2" t="inlineStr">
         <is>
           <t>stone vault, arched ceiling, ancient architecture</t>
         </is>
       </c>
-      <c r="AV10" s="2" t="n">
+      <c r="AX10" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2368,7 +2398,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr">
@@ -2377,127 +2407,135 @@
         </is>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="T11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI11" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [0, 2], [1, 1]]</t>
+        </is>
+      </c>
+      <c r="AJ11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr"/>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF11" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG11" s="2" t="inlineStr">
-        <is>
-          <t>[[0, 0], [0, 1], [0, 2], [1, 1]]</t>
-        </is>
-      </c>
-      <c r="AH11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ11" s="2" t="inlineStr">
+      <c r="AK11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL11" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AK11" s="2" t="inlineStr"/>
-      <c r="AL11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AM11" s="2" t="inlineStr"/>
+      <c r="AN11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AP11" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AQ11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR11" s="2" t="n">
-        <v>1</v>
+      <c r="AQ11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AS11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AT11" s="2" t="n">
+      <c r="AV11" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AU11" s="2" t="inlineStr">
+      <c r="AW11" s="2" t="inlineStr">
         <is>
           <t>dragon lair, cave, mythical den</t>
         </is>
       </c>
-      <c r="AV11" s="2" t="n">
+      <c r="AX11" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2538,7 +2576,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -2554,7 +2592,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr">
@@ -2563,127 +2601,135 @@
         </is>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="T12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>Q +1</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI12" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [0, 2], [1, 0], [1, 1], [1, 2]]</t>
+        </is>
+      </c>
+      <c r="AJ12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>Balanserad</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr"/>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF12" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG12" s="2" t="inlineStr">
-        <is>
-          <t>[[0, 0], [0, 1], [0, 2], [1, 0], [1, 1], [1, 2]]</t>
-        </is>
-      </c>
-      <c r="AH12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ12" s="2" t="inlineStr">
+      <c r="AK12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL12" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AK12" s="2" t="inlineStr"/>
-      <c r="AL12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AM12" s="2" t="inlineStr"/>
+      <c r="AN12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AP12" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AQ12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR12" s="2" t="n">
+      <c r="AQ12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT12" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AS12" s="2" t="n">
+      <c r="AU12" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="AT12" s="2" t="n">
+      <c r="AV12" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AU12" s="2" t="inlineStr">
+      <c r="AW12" s="2" t="inlineStr">
         <is>
           <t>somersault, tumble, playful roll</t>
         </is>
       </c>
-      <c r="AV12" s="2" t="n">
+      <c r="AX12" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2724,7 +2770,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -2740,7 +2786,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr">
@@ -2749,16 +2795,16 @@
         </is>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
@@ -2770,14 +2816,12 @@
           <t>Minsta förskolan; golv på 2 Mkr så att den bär sin ränta.</t>
         </is>
       </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="W13" s="2" t="n">
+        <v>1.5</v>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Q +1</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -2815,34 +2859,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AF13" s="2" t="n">
-        <v>3</v>
+      <c r="AF13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AG13" s="2" t="inlineStr">
         <is>
-          <t>[[0, 1], [1, 0], [1, 1]]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AH13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AI13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ13" s="2" t="inlineStr">
+      <c r="AI13" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 1], [1, 0], [1, 1]]</t>
+        </is>
+      </c>
+      <c r="AJ13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL13" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AK13" s="2" t="inlineStr"/>
-      <c r="AL13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM13" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -2857,23 +2903,31 @@
         </is>
       </c>
       <c r="AQ13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT13" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AS13" s="2" t="n">
+      <c r="AU13" s="2" t="n">
         <v>45.33333333</v>
       </c>
-      <c r="AT13" s="2" t="n">
+      <c r="AV13" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AU13" s="2" t="inlineStr">
+      <c r="AW13" s="2" t="inlineStr">
         <is>
           <t>ladybug, spotted beetle, garden friend</t>
         </is>
       </c>
-      <c r="AV13" s="2" t="n">
+      <c r="AX13" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2926,7 +2980,7 @@
         <v>3</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr">
@@ -2935,127 +2989,135 @@
         </is>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R14" s="2" t="n">
         <v>2</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="T14" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AH14" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI14" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [2, 0], [2, 1], [3, 0], [4, 0]]</t>
+        </is>
+      </c>
+      <c r="AJ14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK14" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>Balanserad</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr"/>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="inlineStr">
-        <is>
-          <t>nivå 2</t>
-        </is>
-      </c>
-      <c r="Y14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z14" s="2" t="inlineStr">
-        <is>
-          <t>nivå 2</t>
-        </is>
-      </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>nivå 2</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD14" s="2" t="inlineStr">
-        <is>
-          <t>nivå 2</t>
-        </is>
-      </c>
-      <c r="AE14" s="2" t="inlineStr">
-        <is>
-          <t>nivå 2</t>
-        </is>
-      </c>
-      <c r="AF14" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG14" s="2" t="inlineStr">
-        <is>
-          <t>[[0, 0], [0, 1], [1, 0], [2, 0], [2, 1], [3, 0], [4, 0]]</t>
-        </is>
-      </c>
-      <c r="AH14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI14" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ14" s="2" t="inlineStr">
+      <c r="AL14" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AK14" s="2" t="n">
+      <c r="AM14" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AL14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM14" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AN14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AO14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AQ14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR14" s="2" t="n">
-        <v>1</v>
+      <c r="AO14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AS14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" s="2" t="n">
         <v>57.5</v>
       </c>
-      <c r="AT14" s="2" t="n">
+      <c r="AV14" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="AU14" s="2" t="inlineStr">
+      <c r="AW14" s="2" t="inlineStr">
         <is>
           <t>rainbow, colorful arc, after rain</t>
         </is>
       </c>
-      <c r="AV14" s="2" t="n">
+      <c r="AX14" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3110,7 +3172,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr">
@@ -3119,16 +3181,16 @@
         </is>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="T15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
@@ -3136,14 +3198,12 @@
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr"/>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="W15" s="2" t="n">
+        <v>1.4</v>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>leverantörskrav installationer nivå 2</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -3158,61 +3218,63 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr">
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="AD15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF15" s="2" t="n">
+      <c r="AF15" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AG15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH15" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AG15" s="2" t="inlineStr">
+      <c r="AI15" s="2" t="inlineStr">
         <is>
           <t>[[0, 0], [1, 0], [1, 1], [2, 0], [2, 1]]</t>
         </is>
       </c>
-      <c r="AH15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ15" s="2" t="inlineStr">
-        <is>
-          <t>prickad</t>
-        </is>
+      <c r="AJ15" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AK15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AL15" s="2" t="n">
-        <v>1</v>
+      <c r="AL15" s="2" t="inlineStr">
+        <is>
+          <t>prickad</t>
+        </is>
       </c>
       <c r="AM15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="AN15" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AO15" s="2" t="n">
         <v>1</v>
@@ -3225,21 +3287,29 @@
       <c r="AQ15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AR15" s="2" t="n">
-        <v>1</v>
+      <c r="AR15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AS15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" s="2" t="n">
         <v>50.4</v>
       </c>
-      <c r="AT15" s="2" t="n">
+      <c r="AV15" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="AU15" s="2" t="inlineStr">
+      <c r="AW15" s="2" t="inlineStr">
         <is>
           <t>treasure chest, golden chest, pirate loot</t>
         </is>
       </c>
-      <c r="AV15" s="2" t="n">
+      <c r="AX15" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3280,7 +3350,7 @@
         <v>2</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>1</v>
@@ -3292,7 +3362,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr">
@@ -3301,127 +3371,135 @@
         </is>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S16" s="2" t="n">
         <v>70</v>
       </c>
       <c r="T16" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>leverantörskrav stomme nivå 2, Q +1</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI16" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [1, 1], [2, 0], [3, 0], [4, 0]]</t>
+        </is>
+      </c>
+      <c r="AJ16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>Balanserad</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr"/>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X16" s="2" t="inlineStr">
-        <is>
-          <t>nivå 2</t>
-        </is>
-      </c>
-      <c r="Y16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z16" s="2" t="inlineStr">
-        <is>
-          <t>nivå 2</t>
-        </is>
-      </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>nivå 2</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD16" s="2" t="inlineStr">
-        <is>
-          <t>nivå 2</t>
-        </is>
-      </c>
-      <c r="AE16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG16" s="2" t="inlineStr">
-        <is>
-          <t>[[0, 0], [0, 1], [1, 0], [1, 1], [2, 0], [3, 0], [4, 0]]</t>
-        </is>
-      </c>
-      <c r="AH16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ16" s="2" t="inlineStr">
+      <c r="AL16" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AK16" s="2" t="n">
+      <c r="AM16" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AL16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM16" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AN16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AO16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AQ16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR16" s="2" t="n">
-        <v>1</v>
+      <c r="AO16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AS16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" s="2" t="n">
         <v>54.28571429</v>
       </c>
-      <c r="AT16" s="2" t="n">
+      <c r="AV16" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="AU16" s="2" t="inlineStr">
+      <c r="AW16" s="2" t="inlineStr">
         <is>
           <t>wild strawberry patch, secret spot, hidden paradise</t>
         </is>
       </c>
-      <c r="AV16" s="2" t="n">
+      <c r="AX16" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3476,7 +3554,7 @@
         <v>1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr">
@@ -3485,16 +3563,16 @@
         </is>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="T17" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
@@ -3502,26 +3580,24 @@
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr"/>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="W17" s="2" t="n">
+        <v>1.3</v>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="Y17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -3547,67 +3623,77 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AF17" s="2" t="n">
+      <c r="AF17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AG17" s="2" t="inlineStr">
+      <c r="AI17" s="2" t="inlineStr">
         <is>
           <t>[[0, 0], [1, 0], [1, 1], [2, 0]]</t>
         </is>
       </c>
-      <c r="AH17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI17" s="2" t="n">
+      <c r="AJ17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AJ17" s="2" t="inlineStr">
+      <c r="AL17" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AK17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL17" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AM17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AO17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AN17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO17" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AP17" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AQ17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR17" s="2" t="n">
+      <c r="AQ17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT17" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AS17" s="2" t="n">
+      <c r="AU17" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="AT17" s="2" t="n">
+      <c r="AV17" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="AU17" s="2" t="inlineStr">
+      <c r="AW17" s="2" t="inlineStr">
         <is>
           <t>star seed, cosmic sprout, celestial growth</t>
         </is>
       </c>
-      <c r="AV17" s="2" t="n">
+      <c r="AX17" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3648,7 +3734,7 @@
         <v>2</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>1</v>
@@ -3660,7 +3746,7 @@
         <v>1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr">
@@ -3669,16 +3755,16 @@
         </is>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
@@ -3686,31 +3772,29 @@
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr"/>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="W18" s="2" t="n">
+        <v>1.4</v>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Q +1</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="Z18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -3718,78 +3802,88 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AD18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF18" s="2" t="n">
+      <c r="AF18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AG18" s="2" t="inlineStr">
+      <c r="AI18" s="2" t="inlineStr">
         <is>
           <t>[[0, 1], [1, 1], [2, 0], [2, 1], [3, 1]]</t>
         </is>
       </c>
-      <c r="AH18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI18" s="2" t="n">
+      <c r="AJ18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AJ18" s="2" t="inlineStr">
+      <c r="AL18" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AK18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AM18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AN18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AO18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AP18" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AQ18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AR18" s="2" t="n">
+      <c r="AR18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT18" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AS18" s="2" t="n">
+      <c r="AU18" s="2" t="n">
         <v>53.6</v>
       </c>
-      <c r="AT18" s="2" t="n">
+      <c r="AV18" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="AU18" s="2" t="inlineStr">
+      <c r="AW18" s="2" t="inlineStr">
         <is>
           <t>enchanted forest, magical woods, fairy tale grove</t>
         </is>
       </c>
-      <c r="AV18" s="2" t="n">
+      <c r="AX18" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3830,7 +3924,7 @@
         <v>2</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>1</v>
@@ -3842,7 +3936,7 @@
         <v>1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr">
@@ -3851,100 +3945,100 @@
         </is>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="T19" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>Q +1, leverantörskrav stomkomplettering nivå 2</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>nivå 3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>nivå 3</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD19" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AE19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF19" s="2" t="inlineStr">
+        <is>
+          <t>nivå 3</t>
+        </is>
+      </c>
+      <c r="AG19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr"/>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X19" s="2" t="inlineStr">
-        <is>
-          <t>nivå 3</t>
-        </is>
-      </c>
-      <c r="Y19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z19" s="2" t="inlineStr">
-        <is>
-          <t>nivå 3</t>
-        </is>
-      </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD19" s="2" t="inlineStr">
-        <is>
-          <t>nivå 3</t>
-        </is>
-      </c>
-      <c r="AE19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF19" s="2" t="n">
+      <c r="AI19" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 1], [0, 3], [1, 0], [1, 1], [1, 2], [1, 3]]</t>
+        </is>
+      </c>
+      <c r="AJ19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AG19" s="2" t="inlineStr">
-        <is>
-          <t>[[0, 1], [0, 3], [1, 0], [1, 1], [1, 2], [1, 3]]</t>
-        </is>
-      </c>
-      <c r="AH19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI19" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ19" s="2" t="inlineStr">
+      <c r="AL19" s="2" t="inlineStr">
         <is>
           <t>prickad</t>
         </is>
       </c>
-      <c r="AK19" s="2" t="n">
+      <c r="AM19" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AL19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AN19" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AO19" s="2" t="n">
         <v>1</v>
@@ -3955,23 +4049,31 @@
         </is>
       </c>
       <c r="AQ19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT19" s="2" t="n">
         <v>1.05</v>
       </c>
-      <c r="AS19" s="2" t="n">
+      <c r="AU19" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="AT19" s="2" t="n">
+      <c r="AV19" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="AU19" s="2" t="inlineStr">
+      <c r="AW19" s="2" t="inlineStr">
         <is>
           <t>coltsfoot flower, early spring bloom, yellow wildflower</t>
         </is>
       </c>
-      <c r="AV19" s="2" t="n">
+      <c r="AX19" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4028,7 +4130,7 @@
         <v>1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr">
@@ -4037,16 +4139,16 @@
         </is>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
@@ -4054,14 +4156,12 @@
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr"/>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="W20" s="2" t="n">
+        <v>1.3</v>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -4099,63 +4199,73 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AF20" s="2" t="n">
-        <v>3</v>
+      <c r="AF20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AG20" s="2" t="inlineStr">
         <is>
-          <t>[[0, 0], [0, 1], [1, 1]]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AH20" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AI20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ20" s="2" t="inlineStr">
+      <c r="AI20" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 1]]</t>
+        </is>
+      </c>
+      <c r="AJ20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL20" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AK20" s="2" t="inlineStr"/>
-      <c r="AL20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM20" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AQ20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AR20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS20" s="2" t="n">
+      <c r="AP20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AT20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" s="2" t="n">
         <v>46.66666667</v>
       </c>
-      <c r="AT20" s="2" t="n">
+      <c r="AV20" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AU20" s="2" t="inlineStr">
+      <c r="AW20" s="2" t="inlineStr">
         <is>
           <t>the pawn, chess piece, opening move</t>
         </is>
       </c>
-      <c r="AV20" s="2" t="n">
+      <c r="AX20" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4196,7 +4306,7 @@
         <v>2</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -4212,7 +4322,7 @@
         <v>1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr">
@@ -4221,7 +4331,7 @@
         </is>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R21" s="2" t="n">
         <v>1</v>
@@ -4230,116 +4340,124 @@
         <v>40</v>
       </c>
       <c r="T21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>Q +1</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH21" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI21" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 1], [2, 0], [2, 1]]</t>
+        </is>
+      </c>
+      <c r="AJ21" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>Balanserad</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr"/>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF21" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG21" s="2" t="inlineStr">
-        <is>
-          <t>[[0, 0], [0, 1], [1, 1], [2, 0], [2, 1]]</t>
-        </is>
-      </c>
-      <c r="AH21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ21" s="2" t="inlineStr">
+      <c r="AK21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL21" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AK21" s="2" t="inlineStr"/>
-      <c r="AL21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM21" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM21" s="2" t="inlineStr"/>
       <c r="AN21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AQ21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AR21" s="2" t="n">
+      <c r="AP21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AT21" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AS21" s="2" t="n">
+      <c r="AU21" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AT21" s="2" t="n">
+      <c r="AV21" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AU21" s="2" t="inlineStr">
+      <c r="AW21" s="2" t="inlineStr">
         <is>
           <t>the queen, chess piece, powerful move</t>
         </is>
       </c>
-      <c r="AV21" s="2" t="n">
+      <c r="AX21" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4380,7 +4498,7 @@
         <v>2</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -4396,7 +4514,7 @@
         <v>1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
@@ -4405,125 +4523,133 @@
         </is>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="T22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>Prestige: dyr att ta fram, svagare i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>Q +1</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH22" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI22" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [1, 1], [2, 0], [2, 1], [2, 2]]</t>
+        </is>
+      </c>
+      <c r="AJ22" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>Prestige: dyr att ta fram, svagare i förvaltningen</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr"/>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF22" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG22" s="2" t="inlineStr">
-        <is>
-          <t>[[0, 0], [0, 1], [1, 0], [1, 1], [2, 0], [2, 1], [2, 2]]</t>
-        </is>
-      </c>
-      <c r="AH22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ22" s="2" t="inlineStr">
+      <c r="AK22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL22" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AK22" s="2" t="inlineStr"/>
-      <c r="AL22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM22" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AO22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AQ22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AR22" s="2" t="n">
+      <c r="AP22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AT22" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AS22" s="2" t="n">
+      <c r="AU22" s="2" t="n">
         <v>41.71428571</v>
       </c>
-      <c r="AT22" s="2" t="n">
+      <c r="AV22" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AU22" s="2" t="inlineStr">
+      <c r="AW22" s="2" t="inlineStr">
         <is>
           <t>the gambit, chess sacrifice, strategic opening</t>
         </is>
       </c>
-      <c r="AV22" s="2" t="n">
+      <c r="AX22" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4578,7 +4704,7 @@
         <v>1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr">
@@ -4587,127 +4713,135 @@
         </is>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S23" s="2" t="n">
         <v>70</v>
       </c>
       <c r="T23" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE23" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AF23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG23" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AH23" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI23" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [1, 0], [1, 1], [2, 0], [2, 1], [3, 0], [4, 0]]</t>
+        </is>
+      </c>
+      <c r="AJ23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>Balanserad</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr"/>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y23" s="2" t="inlineStr">
-        <is>
-          <t>nivå 2</t>
-        </is>
-      </c>
-      <c r="Z23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr">
-        <is>
-          <t>nivå 2</t>
-        </is>
-      </c>
-      <c r="AD23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE23" s="2" t="inlineStr">
-        <is>
-          <t>nivå 2</t>
-        </is>
-      </c>
-      <c r="AF23" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG23" s="2" t="inlineStr">
-        <is>
-          <t>[[0, 0], [1, 0], [1, 1], [2, 0], [2, 1], [3, 0], [4, 0]]</t>
-        </is>
-      </c>
-      <c r="AH23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI23" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ23" s="2" t="inlineStr">
+      <c r="AL23" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AK23" s="2" t="n">
+      <c r="AM23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AL23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM23" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AN23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AQ23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR23" s="2" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AO23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AS23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU23" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="AT23" s="2" t="n">
+      <c r="AV23" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="AU23" s="2" t="inlineStr">
+      <c r="AW23" s="2" t="inlineStr">
         <is>
           <t>the king, chess piece, royal protection</t>
         </is>
       </c>
-      <c r="AV23" s="2" t="n">
+      <c r="AX23" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4764,7 +4898,7 @@
         <v>1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr">
@@ -4773,127 +4907,135 @@
         </is>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="T24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>leverantörskrav installationer nivå 2</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF24" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AG24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH24" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI24" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [1, 0], [1, 1], [2, 0], [2, 1]]</t>
+        </is>
+      </c>
+      <c r="AJ24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK24" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>Balanserad</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr"/>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X24" s="2" t="inlineStr">
-        <is>
-          <t>nivå 2</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z24" s="2" t="inlineStr">
-        <is>
-          <t>nivå 2</t>
-        </is>
-      </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG24" s="2" t="inlineStr">
-        <is>
-          <t>[[0, 0], [1, 0], [1, 1], [2, 0], [2, 1]]</t>
-        </is>
-      </c>
-      <c r="AH24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI24" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ24" s="2" t="inlineStr">
+      <c r="AL24" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AK24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL24" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AM24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AQ24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AR24" s="2" t="n">
+      <c r="AP24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AT24" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AS24" s="2" t="n">
+      <c r="AU24" s="2" t="n">
         <v>48.8</v>
       </c>
-      <c r="AT24" s="2" t="n">
+      <c r="AV24" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="AU24" s="2" t="inlineStr">
+      <c r="AW24" s="2" t="inlineStr">
         <is>
           <t>the bishop, chess piece, diagonal move</t>
         </is>
       </c>
-      <c r="AV24" s="2" t="n">
+      <c r="AX24" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4934,7 +5076,7 @@
         <v>2</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -4950,7 +5092,7 @@
         <v>1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr">
@@ -4959,16 +5101,16 @@
         </is>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
@@ -4976,14 +5118,12 @@
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr"/>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="W25" s="2" t="n">
+        <v>1.5</v>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>leverantörskrav installationer nivå 2, Q +1</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -4998,19 +5138,19 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -5021,67 +5161,77 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AF25" s="2" t="n">
+      <c r="AF25" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AG25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH25" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AG25" s="2" t="inlineStr">
+      <c r="AI25" s="2" t="inlineStr">
         <is>
           <t>[[0, 0], [1, 0], [1, 1], [2, 1]]</t>
         </is>
       </c>
-      <c r="AH25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ25" s="2" t="inlineStr">
+      <c r="AJ25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL25" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AK25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AM25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN25" s="2" t="n">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="AN25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AO25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AQ25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AR25" s="2" t="n">
+      <c r="AP25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AT25" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AS25" s="2" t="n">
+      <c r="AU25" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="AT25" s="2" t="n">
+      <c r="AV25" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="AU25" s="2" t="inlineStr">
+      <c r="AW25" s="2" t="inlineStr">
         <is>
           <t>the countermove, chess response, defensive play</t>
         </is>
       </c>
-      <c r="AV25" s="2" t="n">
+      <c r="AX25" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5138,7 +5288,7 @@
         <v>1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr">
@@ -5147,16 +5297,16 @@
         </is>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T26" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
@@ -5164,14 +5314,12 @@
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr"/>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="W26" s="2" t="n">
+        <v>1.3</v>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
@@ -5186,19 +5334,19 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -5209,31 +5357,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AF26" s="2" t="n">
-        <v>2</v>
+      <c r="AF26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AG26" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI26" s="2" t="inlineStr">
+        <is>
           <t>[[0, 0], [1, 0]]</t>
         </is>
       </c>
-      <c r="AH26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ26" s="2" t="inlineStr">
+      <c r="AJ26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL26" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AK26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL26" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AM26" s="2" t="n">
         <v>1</v>
       </c>
@@ -5243,29 +5395,35 @@
       <c r="AO26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AP26" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AQ26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AR26" s="2" t="n">
-        <v>1</v>
+      <c r="AR26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AS26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU26" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="AT26" s="2" t="n">
+      <c r="AV26" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="AU26" s="2" t="inlineStr">
+      <c r="AW26" s="2" t="inlineStr">
         <is>
           <t>castling, chess maneuver, king safety</t>
         </is>
       </c>
-      <c r="AV26" s="2" t="n">
+      <c r="AX26" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5306,7 +5464,7 @@
         <v>2</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>2</v>
@@ -5320,7 +5478,7 @@
         <v>3</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr">
@@ -5329,127 +5487,135 @@
         </is>
       </c>
       <c r="Q27" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="T27" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>Prestige: dyr att ta fram, svagare i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>Q +1</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>nivå 3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>nivå 3</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>nivå 3</t>
+        </is>
+      </c>
+      <c r="AE27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH27" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI27" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [2, 0], [2, 1], [3, 0], [4, 0], [4, 1]]</t>
+        </is>
+      </c>
+      <c r="AJ27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK27" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL27" s="2" t="inlineStr">
+        <is>
+          <t>streckad</t>
+        </is>
+      </c>
+      <c r="AM27" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="R27" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="S27" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="T27" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>Prestige: dyr att ta fram, svagare i förvaltningen</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr"/>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t>nivå 3</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z27" s="2" t="inlineStr">
-        <is>
-          <t>nivå 3</t>
-        </is>
-      </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>nivå 3</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF27" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG27" s="2" t="inlineStr">
-        <is>
-          <t>[[0, 0], [0, 1], [1, 0], [2, 0], [2, 1], [3, 0], [4, 0], [4, 1]]</t>
-        </is>
-      </c>
-      <c r="AH27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI27" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ27" s="2" t="inlineStr">
-        <is>
-          <t>streckad</t>
-        </is>
-      </c>
-      <c r="AK27" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM27" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AN27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AQ27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AR27" s="2" t="n">
+      <c r="AP27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AT27" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AS27" s="2" t="n">
+      <c r="AU27" s="2" t="n">
         <v>55.5</v>
       </c>
-      <c r="AT27" s="2" t="n">
+      <c r="AV27" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="AU27" s="2" t="inlineStr">
+      <c r="AW27" s="2" t="inlineStr">
         <is>
           <t>the knight, chess piece, L-shaped move</t>
         </is>
       </c>
-      <c r="AV27" s="2" t="n">
+      <c r="AX27" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5490,7 +5656,7 @@
         <v>2</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>1</v>
@@ -5504,7 +5670,7 @@
         <v>1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr">
@@ -5513,16 +5679,16 @@
         </is>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
@@ -5530,14 +5696,12 @@
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr"/>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="W28" s="2" t="n">
+        <v>1.5</v>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Q +1, leverantörskrav stomme nivå 2</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -5552,86 +5716,96 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr">
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE28" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AD28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF28" s="2" t="n">
+      <c r="AF28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH28" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AG28" s="2" t="inlineStr">
+      <c r="AI28" s="2" t="inlineStr">
         <is>
           <t>[[0, 0], [0, 1], [1, 1], [2, 1], [3, 1], [4, 0], [4, 1]]</t>
         </is>
       </c>
-      <c r="AH28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI28" s="2" t="n">
+      <c r="AJ28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK28" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AJ28" s="2" t="inlineStr">
+      <c r="AL28" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AK28" s="2" t="n">
+      <c r="AM28" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AL28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM28" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AN28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AP28" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AQ28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AR28" s="2" t="n">
+      <c r="AR28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT28" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AS28" s="2" t="n">
+      <c r="AU28" s="2" t="n">
         <v>54.85714286</v>
       </c>
-      <c r="AT28" s="2" t="n">
+      <c r="AV28" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="AU28" s="2" t="inlineStr">
+      <c r="AW28" s="2" t="inlineStr">
         <is>
           <t>the rook, chess piece, straight power</t>
         </is>
       </c>
-      <c r="AV28" s="2" t="n">
+      <c r="AX28" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5686,7 +5860,7 @@
         <v>1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr">
@@ -5695,125 +5869,133 @@
         </is>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S29" s="2" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI29" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [1, 0], [1, 1], [2, 0]]</t>
+        </is>
+      </c>
+      <c r="AJ29" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr"/>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF29" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG29" s="2" t="inlineStr">
-        <is>
-          <t>[[0, 0], [1, 0], [1, 1], [2, 0]]</t>
-        </is>
-      </c>
-      <c r="AH29" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ29" s="2" t="inlineStr">
+      <c r="AK29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL29" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AK29" s="2" t="inlineStr"/>
-      <c r="AL29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN29" s="2" t="n">
-        <v>1</v>
+      <c r="AM29" s="2" t="inlineStr"/>
+      <c r="AN29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AO29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AP29" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AQ29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AR29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AS29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AT29" s="2" t="n">
+      <c r="AV29" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AU29" s="2" t="inlineStr">
+      <c r="AW29" s="2" t="inlineStr">
         <is>
           <t>galaxy, spiral nebula, cosmic swirl</t>
         </is>
       </c>
-      <c r="AV29" s="2" t="n">
+      <c r="AX29" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5854,7 +6036,7 @@
         <v>1</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -5868,7 +6050,7 @@
         <v>1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr">
@@ -5877,125 +6059,133 @@
         </is>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="T30" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>Q +1</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH30" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI30" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 2], [1, 0], [1, 1], [1, 2], [2, 0], [2, 1]]</t>
+        </is>
+      </c>
+      <c r="AJ30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>Balanserad</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr"/>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF30" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG30" s="2" t="inlineStr">
-        <is>
-          <t>[[0, 2], [1, 0], [1, 1], [1, 2], [2, 0], [2, 1]]</t>
-        </is>
-      </c>
-      <c r="AH30" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ30" s="2" t="inlineStr">
+      <c r="AK30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL30" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AK30" s="2" t="inlineStr"/>
-      <c r="AL30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN30" s="2" t="n">
-        <v>1</v>
+      <c r="AM30" s="2" t="inlineStr"/>
+      <c r="AN30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AO30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AP30" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AQ30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT30" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AS30" s="2" t="n">
+      <c r="AU30" s="2" t="n">
         <v>43.33333333</v>
       </c>
-      <c r="AT30" s="2" t="n">
+      <c r="AV30" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AU30" s="2" t="inlineStr">
+      <c r="AW30" s="2" t="inlineStr">
         <is>
           <t>lighthouse, beacon tower, guiding light</t>
         </is>
       </c>
-      <c r="AV30" s="2" t="n">
+      <c r="AX30" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6036,7 +6226,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -6050,7 +6240,7 @@
         <v>1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr">
@@ -6059,16 +6249,16 @@
         </is>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R31" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S31" s="2" t="n">
         <v>60</v>
       </c>
       <c r="T31" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
@@ -6076,14 +6266,12 @@
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="W31" s="2" t="n">
+        <v>1.5</v>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Q +1</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -6121,63 +6309,73 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AF31" s="2" t="n">
+      <c r="AF31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH31" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AG31" s="2" t="inlineStr">
+      <c r="AI31" s="2" t="inlineStr">
         <is>
           <t>[[0, 0], [0, 1], [1, 0], [1, 1], [1, 2], [2, 0], [2, 1], [2, 2]]</t>
         </is>
       </c>
-      <c r="AH31" s="2" t="n">
+      <c r="AJ31" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AI31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ31" s="2" t="inlineStr">
+      <c r="AK31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL31" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AK31" s="2" t="inlineStr"/>
-      <c r="AL31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN31" s="2" t="n">
-        <v>2</v>
+      <c r="AM31" s="2" t="inlineStr"/>
+      <c r="AN31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AO31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AP31" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AQ31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AR31" s="2" t="n">
+      <c r="AR31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT31" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AS31" s="2" t="n">
+      <c r="AU31" s="2" t="n">
         <v>41.5</v>
       </c>
-      <c r="AT31" s="2" t="n">
+      <c r="AV31" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="AU31" s="2" t="inlineStr">
+      <c r="AW31" s="2" t="inlineStr">
         <is>
           <t>bastion, fortified tower, stronghold</t>
         </is>
       </c>
-      <c r="AV31" s="2" t="n">
+      <c r="AX31" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6234,7 +6432,7 @@
         <v>1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr">
@@ -6243,16 +6441,16 @@
         </is>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
@@ -6260,26 +6458,24 @@
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr"/>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="W32" s="2" t="n">
+        <v>1.3</v>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="Y32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -6287,83 +6483,93 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="AC32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AE32" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF32" s="2" t="n">
+      <c r="AF32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH32" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AG32" s="2" t="inlineStr">
+      <c r="AI32" s="2" t="inlineStr">
         <is>
           <t>[[0, 0], [0, 1], [1, 0], [1, 1], [2, 0]]</t>
         </is>
       </c>
-      <c r="AH32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI32" s="2" t="n">
+      <c r="AJ32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AJ32" s="2" t="inlineStr">
+      <c r="AL32" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AK32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AM32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AN32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AO32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AP32" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AQ32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AR32" s="2" t="n">
-        <v>1</v>
+      <c r="AR32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AS32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" s="2" t="n">
         <v>48.8</v>
       </c>
-      <c r="AT32" s="2" t="n">
+      <c r="AV32" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="AU32" s="2" t="inlineStr">
+      <c r="AW32" s="2" t="inlineStr">
         <is>
           <t>nebula, cosmic cloud, star nursery</t>
         </is>
       </c>
-      <c r="AV32" s="2" t="n">
+      <c r="AX32" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6418,7 +6624,7 @@
         <v>1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr">
@@ -6427,131 +6633,139 @@
         </is>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S33" s="2" t="n">
         <v>70</v>
       </c>
       <c r="T33" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Tvilling med Kometbanan i Projektutvecklingen, men C i stället för D — samma pris, bättre förvaltning.</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>leverantörskrav gemensamma arbeten nivå 2</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>nivå 3</t>
+        </is>
+      </c>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE33" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AF33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG33" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AH33" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI33" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [0, 2], [0, 3], [1, 0], [1, 1], [2, 0]]</t>
+        </is>
+      </c>
+      <c r="AJ33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK33" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>Balanserad</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Tvilling med Kometbanan i Projektutvecklingen, men C i stället för D — samma pris, bättre förvaltning.</t>
-        </is>
-      </c>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y33" s="2" t="inlineStr">
-        <is>
-          <t>nivå 2</t>
-        </is>
-      </c>
-      <c r="Z33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>nivå 3</t>
-        </is>
-      </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr">
-        <is>
-          <t>nivå 2</t>
-        </is>
-      </c>
-      <c r="AD33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF33" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG33" s="2" t="inlineStr">
-        <is>
-          <t>[[0, 0], [0, 1], [0, 2], [0, 3], [1, 0], [1, 1], [2, 0]]</t>
-        </is>
-      </c>
-      <c r="AH33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI33" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ33" s="2" t="inlineStr">
+      <c r="AL33" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AK33" s="2" t="n">
+      <c r="AM33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AL33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN33" s="2" t="n">
-        <v>1</v>
+      <c r="AN33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AO33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AP33" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AQ33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT33" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AS33" s="2" t="n">
+      <c r="AU33" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="AT33" s="2" t="n">
+      <c r="AV33" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="AU33" s="2" t="inlineStr">
+      <c r="AW33" s="2" t="inlineStr">
         <is>
           <t>quadrant, navigation instrument, star chart</t>
         </is>
       </c>
-      <c r="AV33" s="2" t="n">
+      <c r="AX33" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6592,7 +6806,7 @@
         <v>2</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>1</v>
@@ -6606,7 +6820,7 @@
         <v>1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr">
@@ -6615,16 +6829,16 @@
         </is>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S34" s="2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="T34" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
@@ -6632,108 +6846,116 @@
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr"/>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="W34" s="2" t="n">
+        <v>1.5</v>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>leverantörskrav mark nivå 2, Q +1</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>nivå 2</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB34" s="2" t="inlineStr">
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD34" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="AC34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD34" s="2" t="inlineStr">
+      <c r="AE34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF34" s="2" t="inlineStr">
         <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="AE34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF34" s="2" t="n">
+      <c r="AG34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH34" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AG34" s="2" t="inlineStr">
+      <c r="AI34" s="2" t="inlineStr">
         <is>
           <t>[[0, 1], [0, 2], [0, 3], [1, 0], [1, 1], [1, 3], [2, 0]]</t>
         </is>
       </c>
-      <c r="AH34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI34" s="2" t="n">
+      <c r="AJ34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK34" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AJ34" s="2" t="inlineStr">
+      <c r="AL34" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AK34" s="2" t="n">
+      <c r="AM34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AL34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM34" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AN34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AO34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AP34" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AQ34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AR34" s="2" t="n">
+      <c r="AR34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT34" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AS34" s="2" t="n">
+      <c r="AU34" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="AT34" s="2" t="n">
+      <c r="AV34" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="AU34" s="2" t="inlineStr">
+      <c r="AW34" s="2" t="inlineStr">
         <is>
           <t>comet path, orbital trail, stellar trajectory</t>
         </is>
       </c>
-      <c r="AV34" s="2" t="n">
+      <c r="AX34" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6788,7 +7010,7 @@
         <v>4</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr">
@@ -6797,127 +7019,135 @@
         </is>
       </c>
       <c r="Q35" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>nivå 3</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>nivå 3</t>
+        </is>
+      </c>
+      <c r="AE35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF35" s="2" t="inlineStr">
+        <is>
+          <t>nivå 3</t>
+        </is>
+      </c>
+      <c r="AG35" s="2" t="inlineStr">
+        <is>
+          <t>nivå 3</t>
+        </is>
+      </c>
+      <c r="AH35" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI35" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [0, 2], [0, 3], [1, 0], [1, 3], [2, 0], [2, 3]]</t>
+        </is>
+      </c>
+      <c r="AJ35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK35" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL35" s="2" t="inlineStr">
+        <is>
+          <t>streckad</t>
+        </is>
+      </c>
+      <c r="AM35" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="R35" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="S35" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="T35" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>Balanserad</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr"/>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y35" s="2" t="inlineStr">
-        <is>
-          <t>nivå 3</t>
-        </is>
-      </c>
-      <c r="Z35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>nivå 3</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD35" s="2" t="inlineStr">
-        <is>
-          <t>nivå 3</t>
-        </is>
-      </c>
-      <c r="AE35" s="2" t="inlineStr">
-        <is>
-          <t>nivå 3</t>
-        </is>
-      </c>
-      <c r="AF35" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG35" s="2" t="inlineStr">
-        <is>
-          <t>[[0, 0], [0, 1], [0, 2], [0, 3], [1, 0], [1, 3], [2, 0], [2, 3]]</t>
-        </is>
-      </c>
-      <c r="AH35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI35" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ35" s="2" t="inlineStr">
-        <is>
-          <t>streckad</t>
-        </is>
-      </c>
-      <c r="AK35" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN35" s="2" t="n">
-        <v>1</v>
+      <c r="AN35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AO35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AP35" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AQ35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AR35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AS35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" s="2" t="n">
         <v>58.5</v>
       </c>
-      <c r="AT35" s="2" t="n">
+      <c r="AV35" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="AU35" s="2" t="inlineStr">
+      <c r="AW35" s="2" t="inlineStr">
         <is>
           <t>star harbor, celestial port, cosmic dock</t>
         </is>
       </c>
-      <c r="AV35" s="2" t="n">
+      <c r="AX35" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6958,7 +7188,7 @@
         <v>3</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>2</v>
@@ -6972,7 +7202,7 @@
         <v>3</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr">
@@ -6981,16 +7211,16 @@
         </is>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R36" s="2" t="n">
         <v>2</v>
       </c>
       <c r="S36" s="2" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="T36" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
@@ -6998,14 +7228,12 @@
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr"/>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="W36" s="2" t="n">
+        <v>1.4</v>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Q +1</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -7030,76 +7258,86 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE36" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AD36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE36" s="2" t="inlineStr">
+      <c r="AF36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG36" s="2" t="inlineStr">
         <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AF36" s="2" t="n">
+      <c r="AH36" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AG36" s="2" t="inlineStr">
+      <c r="AI36" s="2" t="inlineStr">
         <is>
           <t>[[0, 3], [1, 3], [2, 1], [2, 3], [3, 0], [3, 1], [3, 2], [3, 3]]</t>
         </is>
       </c>
-      <c r="AH36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI36" s="2" t="n">
+      <c r="AJ36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK36" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AJ36" s="2" t="inlineStr">
+      <c r="AL36" s="2" t="inlineStr">
         <is>
           <t>streckad</t>
         </is>
       </c>
-      <c r="AK36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL36" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AM36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AO36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AP36" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AQ36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT36" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AS36" s="2" t="n">
+      <c r="AU36" s="2" t="n">
         <v>55.5</v>
       </c>
-      <c r="AT36" s="2" t="n">
+      <c r="AV36" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="AU36" s="2" t="inlineStr">
+      <c r="AW36" s="2" t="inlineStr">
         <is>
           <t>space axis, cosmic alignment, stellar center</t>
         </is>
       </c>
-      <c r="AV36" s="2" t="n">
+      <c r="AX36" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7154,7 +7392,7 @@
         <v>4</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="O37" s="2" t="inlineStr"/>
       <c r="P37" s="2" t="inlineStr">
@@ -7163,127 +7401,135 @@
         </is>
       </c>
       <c r="Q37" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>leverantörskrav mark nivå 2</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH37" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI37" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 3], [1, 3], [2, 2], [2, 3], [3, 0], [3, 1], [3, 2], [3, 3]]</t>
+        </is>
+      </c>
+      <c r="AJ37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK37" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL37" s="2" t="inlineStr">
+        <is>
+          <t>streckad</t>
+        </is>
+      </c>
+      <c r="AM37" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="R37" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="S37" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="T37" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>Balanserad</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr"/>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF37" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG37" s="2" t="inlineStr">
-        <is>
-          <t>[[0, 3], [1, 3], [2, 2], [2, 3], [3, 0], [3, 1], [3, 2], [3, 3]]</t>
-        </is>
-      </c>
-      <c r="AH37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI37" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ37" s="2" t="inlineStr">
-        <is>
-          <t>streckad</t>
-        </is>
-      </c>
-      <c r="AK37" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN37" s="2" t="n">
-        <v>2</v>
+      <c r="AN37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AO37" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AP37" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AQ37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT37" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AS37" s="2" t="n">
+      <c r="AU37" s="2" t="n">
         <v>59.5</v>
       </c>
-      <c r="AT37" s="2" t="n">
+      <c r="AV37" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="AU37" s="2" t="inlineStr">
+      <c r="AW37" s="2" t="inlineStr">
         <is>
           <t>observatory, telescope dome, stargazing</t>
         </is>
       </c>
-      <c r="AV37" s="2" t="n">
+      <c r="AX37" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7340,7 +7586,7 @@
         <v>1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr">
@@ -7349,16 +7595,16 @@
         </is>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S38" s="2" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T38" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
@@ -7370,14 +7616,12 @@
           <t>Instegsprojektet som blir spelets kassako i förvaltningen — låg yield på bostäder.</t>
         </is>
       </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="W38" s="2" t="n">
+        <v>1.3</v>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -7415,65 +7659,75 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AF38" s="2" t="n">
-        <v>3</v>
+      <c r="AF38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AG38" s="2" t="inlineStr">
         <is>
-          <t>[[0, 0], [0, 1], [1, 0]]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AH38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AI38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ38" s="2" t="inlineStr">
+      <c r="AI38" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0]]</t>
+        </is>
+      </c>
+      <c r="AJ38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL38" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AK38" s="2" t="inlineStr"/>
-      <c r="AL38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AQ38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR38" s="2" t="n">
-        <v>1</v>
+      <c r="AM38" s="2" t="inlineStr"/>
+      <c r="AN38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AS38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" s="2" t="n">
         <v>45.33333333</v>
       </c>
-      <c r="AT38" s="2" t="n">
+      <c r="AV38" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AU38" s="2" t="inlineStr">
+      <c r="AW38" s="2" t="inlineStr">
         <is>
           <t>harbor change, port transition, dock shift</t>
         </is>
       </c>
-      <c r="AV38" s="2" t="n">
+      <c r="AX38" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7514,7 +7768,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -7530,7 +7784,7 @@
         <v>1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr">
@@ -7539,16 +7793,16 @@
         </is>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S39" s="2" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="T39" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
@@ -7556,14 +7810,12 @@
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr"/>
-      <c r="W39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="W39" s="2" t="n">
+        <v>1.4</v>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Q +1</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -7601,65 +7853,75 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AF39" s="2" t="n">
+      <c r="AF39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH39" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AG39" s="2" t="inlineStr">
+      <c r="AI39" s="2" t="inlineStr">
         <is>
           <t>[[0, 1], [0, 2], [1, 0], [1, 1], [1, 2]]</t>
         </is>
       </c>
-      <c r="AH39" s="2" t="n">
+      <c r="AJ39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AI39" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ39" s="2" t="inlineStr">
+      <c r="AK39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL39" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AK39" s="2" t="inlineStr"/>
-      <c r="AL39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN39" s="2" t="n">
-        <v>2</v>
+      <c r="AM39" s="2" t="inlineStr"/>
+      <c r="AN39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AO39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AQ39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AR39" s="2" t="n">
+      <c r="AP39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AT39" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AS39" s="2" t="n">
+      <c r="AU39" s="2" t="n">
         <v>42.4</v>
       </c>
-      <c r="AT39" s="2" t="n">
+      <c r="AV39" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="AU39" s="2" t="inlineStr">
+      <c r="AW39" s="2" t="inlineStr">
         <is>
           <t>birdsong, avian melody, morning chorus</t>
         </is>
       </c>
-      <c r="AV39" s="2" t="n">
+      <c r="AX39" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7700,7 +7962,7 @@
         <v>1</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -7716,7 +7978,7 @@
         <v>1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr">
@@ -7725,129 +7987,137 @@
         </is>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S40" s="2" t="n">
         <v>50</v>
       </c>
       <c r="T40" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>Q +1</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH40" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI40" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [1, 1], [2, 0], [2, 1]]</t>
+        </is>
+      </c>
+      <c r="AJ40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>Balanserad</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr"/>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>nivå 2</t>
-        </is>
-      </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF40" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG40" s="2" t="inlineStr">
-        <is>
-          <t>[[0, 0], [0, 1], [1, 0], [1, 1], [2, 0], [2, 1]]</t>
-        </is>
-      </c>
-      <c r="AH40" s="2" t="n">
+      <c r="AK40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL40" s="2" t="inlineStr">
+        <is>
+          <t>heldragen</t>
+        </is>
+      </c>
+      <c r="AM40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AI40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ40" s="2" t="inlineStr">
-        <is>
-          <t>heldragen</t>
-        </is>
-      </c>
-      <c r="AK40" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AQ40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR40" s="2" t="n">
+      <c r="AN40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT40" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AS40" s="2" t="n">
+      <c r="AU40" s="2" t="n">
         <v>47.33333333</v>
       </c>
-      <c r="AT40" s="2" t="n">
+      <c r="AV40" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="AU40" s="2" t="inlineStr">
+      <c r="AW40" s="2" t="inlineStr">
         <is>
           <t>mountain slope, hillside, rocky incline</t>
         </is>
       </c>
-      <c r="AV40" s="2" t="n">
+      <c r="AX40" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7902,7 +8172,7 @@
         <v>1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr">
@@ -7911,16 +8181,16 @@
         </is>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S41" s="2" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="T41" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
@@ -7932,14 +8202,12 @@
           <t>Liten hyresrätt; dämpad så att inte alla små hyresrätter blir kassakor.</t>
         </is>
       </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="W41" s="2" t="n">
+        <v>1.3</v>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -7964,80 +8232,90 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE41" s="2" t="inlineStr">
+        <is>
           <t>nivå 2</t>
         </is>
       </c>
-      <c r="AD41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF41" s="2" t="n">
+      <c r="AF41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH41" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AG41" s="2" t="inlineStr">
+      <c r="AI41" s="2" t="inlineStr">
         <is>
           <t>[[0, 0], [0, 1], [1, 0]]</t>
         </is>
       </c>
-      <c r="AH41" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ41" s="2" t="inlineStr">
+      <c r="AJ41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL41" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AK41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AM41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AN41" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AM41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP41" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AQ41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AR41" s="2" t="n">
-        <v>1</v>
+      <c r="AR41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AS41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU41" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="AT41" s="2" t="n">
+      <c r="AV41" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="AU41" s="2" t="inlineStr">
+      <c r="AW41" s="2" t="inlineStr">
         <is>
           <t>rose grove, flowering garden, romantic park</t>
         </is>
       </c>
-      <c r="AV41" s="2" t="n">
+      <c r="AX41" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8092,7 +8370,7 @@
         <v>1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr">
@@ -8101,129 +8379,137 @@
         </is>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S42" s="2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="T42" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>Balanserad</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr"/>
+      <c r="W42" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>leverantörskrav ytskikt nivå 2</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AE42" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AF42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH42" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI42" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [0, 2], [1, 1], [1, 2]]</t>
+        </is>
+      </c>
+      <c r="AJ42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>Balanserad</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr"/>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>nivå 2</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF42" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG42" s="2" t="inlineStr">
-        <is>
-          <t>[[0, 0], [0, 1], [0, 2], [1, 1], [1, 2]]</t>
-        </is>
-      </c>
-      <c r="AH42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI42" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ42" s="2" t="inlineStr">
+      <c r="AL42" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AK42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AM42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AN42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AQ42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR42" s="2" t="n">
+      <c r="AN42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT42" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AS42" s="2" t="n">
+      <c r="AU42" s="2" t="n">
         <v>49.6</v>
       </c>
-      <c r="AT42" s="2" t="n">
+      <c r="AV42" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="AU42" s="2" t="inlineStr">
+      <c r="AW42" s="2" t="inlineStr">
         <is>
           <t>leaf meadow, deciduous clearing, green pasture</t>
         </is>
       </c>
-      <c r="AV42" s="2" t="n">
+      <c r="AX42" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8261,7 +8547,7 @@
         <v>78</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>2</v>
@@ -8278,7 +8564,7 @@
         <v>1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr">
@@ -8287,127 +8573,135 @@
         </is>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R43" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S43" s="2" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="T43" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>leverantörskrav mark nivå 2, H +1</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>nivå 3</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG43" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AH43" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI43" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [1, 1], [2, 0], [3, 0]]</t>
+        </is>
+      </c>
+      <c r="AJ43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK43" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr"/>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y43" s="2" t="inlineStr">
-        <is>
-          <t>nivå 2</t>
-        </is>
-      </c>
-      <c r="Z43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>nivå 3</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE43" s="2" t="inlineStr">
-        <is>
-          <t>nivå 2</t>
-        </is>
-      </c>
-      <c r="AF43" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG43" s="2" t="inlineStr">
-        <is>
-          <t>[[0, 0], [0, 1], [1, 0], [1, 1], [2, 0], [3, 0]]</t>
-        </is>
-      </c>
-      <c r="AH43" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI43" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ43" s="2" t="inlineStr">
+      <c r="AL43" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AK43" s="2" t="n">
+      <c r="AM43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AL43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM43" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AN43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AO43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AQ43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR43" s="2" t="n">
+      <c r="AO43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT43" s="2" t="n">
         <v>0.9</v>
       </c>
-      <c r="AS43" s="2" t="n">
+      <c r="AU43" s="2" t="n">
         <v>51.33333333</v>
       </c>
-      <c r="AT43" s="2" t="n">
+      <c r="AV43" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="AU43" s="2" t="inlineStr">
+      <c r="AW43" s="2" t="inlineStr">
         <is>
           <t>mill hill, grinding slope, water mill</t>
         </is>
       </c>
-      <c r="AV43" s="2" t="n">
+      <c r="AX43" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8462,7 +8756,7 @@
         <v>1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr">
@@ -8471,16 +8765,16 @@
         </is>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S44" s="2" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="T44" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
@@ -8492,41 +8786,39 @@
           <t>Liten hyresrätt; dämpad så att inte alla små hyresrätter blir kassakor.</t>
         </is>
       </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="W44" s="2" t="n">
+        <v>1.3</v>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="Y44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AB44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -8534,68 +8826,78 @@
       </c>
       <c r="AE44" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG44" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AF44" s="2" t="n">
+      <c r="AH44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AG44" s="2" t="inlineStr">
+      <c r="AI44" s="2" t="inlineStr">
         <is>
           <t>[[0, 0], [0, 1], [1, 1]]</t>
         </is>
       </c>
-      <c r="AH44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ44" s="2" t="inlineStr">
+      <c r="AJ44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL44" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AK44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AM44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AN44" s="2" t="n">
-        <v>1</v>
+      <c r="AN44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AO44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AP44" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AQ44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AR44" s="2" t="n">
-        <v>1</v>
+      <c r="AR44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AS44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU44" s="2" t="n">
         <v>50.66666667</v>
       </c>
-      <c r="AT44" s="2" t="n">
+      <c r="AV44" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="AU44" s="2" t="inlineStr">
+      <c r="AW44" s="2" t="inlineStr">
         <is>
           <t>river bank, stream edge, waterside</t>
         </is>
       </c>
-      <c r="AV44" s="2" t="n">
+      <c r="AX44" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8636,7 +8938,7 @@
         <v>2</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>2</v>
@@ -8648,7 +8950,7 @@
         <v>4</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>175</v>
+        <v>250</v>
       </c>
       <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr">
@@ -8657,127 +8959,135 @@
         </is>
       </c>
       <c r="Q45" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S45" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="T45" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>Q +1</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>nivå 3</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>nivå 3</t>
+        </is>
+      </c>
+      <c r="AE45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF45" s="2" t="inlineStr">
+        <is>
+          <t>nivå 3</t>
+        </is>
+      </c>
+      <c r="AG45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH45" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI45" s="2" t="inlineStr">
+        <is>
+          <t>[[0, 0], [0, 1], [1, 0], [2, 0], [3, 0], [3, 1], [3, 2], [3, 3]]</t>
+        </is>
+      </c>
+      <c r="AJ45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK45" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL45" s="2" t="inlineStr">
+        <is>
+          <t>heldragen</t>
+        </is>
+      </c>
+      <c r="AM45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="R45" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="S45" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="T45" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>Kassako: billig att ta fram, stark i förvaltningen</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr"/>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y45" s="2" t="inlineStr">
-        <is>
-          <t>nivå 3</t>
-        </is>
-      </c>
-      <c r="Z45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr">
-        <is>
-          <t>nivå 3</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD45" s="2" t="inlineStr">
-        <is>
-          <t>nivå 3</t>
-        </is>
-      </c>
-      <c r="AE45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF45" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG45" s="2" t="inlineStr">
-        <is>
-          <t>[[0, 0], [0, 1], [1, 0], [2, 0], [3, 0], [3, 1], [3, 2], [3, 3]]</t>
-        </is>
-      </c>
-      <c r="AH45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI45" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ45" s="2" t="inlineStr">
-        <is>
-          <t>heldragen</t>
-        </is>
-      </c>
-      <c r="AK45" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM45" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AN45" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AQ45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT45" s="2" t="n">
         <v>1.05</v>
       </c>
-      <c r="AS45" s="2" t="n">
+      <c r="AU45" s="2" t="n">
         <v>56.5</v>
       </c>
-      <c r="AT45" s="2" t="n">
+      <c r="AV45" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="AU45" s="2" t="inlineStr">
+      <c r="AW45" s="2" t="inlineStr">
         <is>
           <t>stone edge, rock ridge, granite brow</t>
         </is>
       </c>
-      <c r="AV45" s="2" t="n">
+      <c r="AX45" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8830,25 +9140,25 @@
         <v>1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="O46" s="2" t="inlineStr"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Q46" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R46" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S46" s="2" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="T46" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
@@ -8860,14 +9170,12 @@
           <t>Stort hållbart projekt; C i stället för D (texten nämner ingen energiklass).</t>
         </is>
       </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="W46" s="2" t="n">
+        <v>1.5</v>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>energiklass C → D, leverantörskrav stomme nivå 2</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -8877,19 +9185,19 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>nivå 2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -8902,68 +9210,78 @@
       </c>
       <c r="AE46" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG46" s="2" t="inlineStr">
+        <is>
           <t>nivå 3</t>
         </is>
       </c>
-      <c r="AF46" s="2" t="n">
+      <c r="AH46" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AG46" s="2" t="inlineStr">
+      <c r="AI46" s="2" t="inlineStr">
         <is>
           <t>[[0, 3], [1, 1], [1, 3], [2, 0], [2, 1], [2, 2], [2, 3]]</t>
         </is>
       </c>
-      <c r="AH46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI46" s="2" t="n">
+      <c r="AJ46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK46" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AJ46" s="2" t="inlineStr">
+      <c r="AL46" s="2" t="inlineStr">
         <is>
           <t>heldragen</t>
         </is>
       </c>
-      <c r="AK46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AM46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN46" s="2" t="n">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="AN46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AO46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AP46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AP46" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AQ46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AR46" s="2" t="n">
+      <c r="AR46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AS46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT46" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="AS46" s="2" t="n">
+      <c r="AU46" s="2" t="n">
         <v>53.71428571</v>
       </c>
-      <c r="AT46" s="2" t="n">
+      <c r="AV46" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="AU46" s="2" t="inlineStr">
+      <c r="AW46" s="2" t="inlineStr">
         <is>
           <t>lake glimmer, water sparkle, shimmering shore</t>
         </is>
       </c>
-      <c r="AV46" s="2" t="n">
+      <c r="AX46" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12290,7 +12608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -12701,7 +13019,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NYTT. Ej BRF. 3 % av lånet, fast i grundspelet</t>
+          <t>NYTT. Ej BRF. 2 % av lånet (minst 1), fast i grundspelet</t>
         </is>
       </c>
     </row>
@@ -12723,7 +13041,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NYTT. Ej BRF. 70 % av MV vid start, avrundat till 10</t>
+          <t>NYTT. Ej BRF. 70 % av anskaffningen, avrundat till 5</t>
         </is>
       </c>
     </row>
@@ -12796,56 +13114,56 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nivåkrav Mark</t>
+          <t>MV-faktor</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MARK</t>
+          <t>F_faktor</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nej</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>'-' = inget krav</t>
+          <t>Ej tryckt — omräkningen 2026-09-27: MV × 1,3–1,5 mot förvaltningsvärdet</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nivåkrav Husunderbyggnad</t>
+          <t>Motvikt</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HUSUNDERBYGGNAD</t>
+          <t>F_motvikt</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nej</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>'-' = inget krav</t>
+          <t>Ej tryckt — det som gjorts svårare på kort med faktor 1,4–1,5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nivåkrav Stomme</t>
+          <t>Nivåkrav Mark</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>STOMME</t>
+          <t>MARK</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -12862,12 +13180,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nivåkrav Yttertak</t>
+          <t>Nivåkrav Husunderbyggnad</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>YTTERTAK</t>
+          <t>HUSUNDERBYGGNAD</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -12884,12 +13202,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nivåkrav Fasader</t>
+          <t>Nivåkrav Stomme</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FASADER</t>
+          <t>STOMME</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -12906,12 +13224,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nivåkrav Stomkomplettering</t>
+          <t>Nivåkrav Yttertak</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>STOMKOMPLETTERING</t>
+          <t>YTTERTAK</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -12928,12 +13246,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nivåkrav Ytskikt</t>
+          <t>Nivåkrav Fasader</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>INV YTSKIKT</t>
+          <t>FASADER</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -12950,12 +13268,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nivåkrav Installationer</t>
+          <t>Nivåkrav Stomkomplettering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>INSTALLATIONER</t>
+          <t>STOMKOMPLETTERING</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -12972,12 +13290,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nivåkrav Gemensamma arbeten</t>
+          <t>Nivåkrav Ytskikt</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GEMENSAMMA ARBETEN</t>
+          <t>INV YTSKIKT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -12994,56 +13312,56 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Antal rutor</t>
+          <t>Nivåkrav Installationer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>F_rutor</t>
+          <t>INSTALLATIONER</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nej</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ej tryckt — brickans storlek; en ruta = 250 kvm (= BTA / 250)</t>
+          <t>'-' = inget krav</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Form (rutor)</t>
+          <t>Nivåkrav Gemensamma arbeten</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>F_form</t>
+          <t>GEMENSAMMA ARBETEN</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nej</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ej tryckt — brickans form som [rad, kolumn] per ruta (från brickorna)</t>
+          <t>'-' = inget krav</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Förekomst</t>
+          <t>Antal rutor</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Förekomst</t>
+          <t>F_rutor</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -13053,19 +13371,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ej tryckt — speldata</t>
+          <t>Ej tryckt — brickans storlek; en ruta = 250 kvm (= BTA / 250)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Formfaktor</t>
+          <t>Form (rutor)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Formfaktor</t>
+          <t>F_form</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -13075,19 +13393,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ej tryckt — styr brickans form (1–8)</t>
+          <t>Ej tryckt — brickans form som [rad, kolumn] per ruta (från brickorna)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Linjetyp</t>
+          <t>Förekomst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>linjetyp</t>
+          <t>Förekomst</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -13097,19 +13415,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ej tryckt — ramens linjestil</t>
+          <t>Ej tryckt — speldata</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Antal krav</t>
+          <t>Formfaktor</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Antal krav</t>
+          <t>Formfaktor</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -13119,19 +13437,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ej tryckt</t>
+          <t>Ej tryckt — styr brickans form (1–8)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>Linjetyp</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>STA</t>
+          <t>linjetyp</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -13141,19 +13459,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ej tryckt — kompetens</t>
+          <t>Ej tryckt — ramens linjestil</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KOM</t>
+          <t>Antal krav</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KOM</t>
+          <t>Antal krav</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -13163,19 +13481,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ej tryckt — kompetens</t>
+          <t>Ej tryckt</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>STA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -13192,12 +13510,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NOG</t>
+          <t>KOM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NOG</t>
+          <t>KOM</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -13214,12 +13532,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>INN</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>INN</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -13236,12 +13554,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ABM</t>
+          <t>NOG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ABM</t>
+          <t>NOG</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -13258,12 +13576,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Skalfaktor</t>
+          <t>INN</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Skalfaktor</t>
+          <t>INN</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -13273,19 +13591,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ej tryckt</t>
+          <t>Ej tryckt — kompetens</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Intäkt/kvm nu</t>
+          <t>ABM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>intäkt/kvm nu</t>
+          <t>ABM</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -13295,19 +13613,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ej tryckt — beräkningsunderlag</t>
+          <t>Ej tryckt — kompetens</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Förslag intäkt</t>
+          <t>Skalfaktor</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>förslag intäkt</t>
+          <t>Skalfaktor</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -13317,19 +13635,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ej tryckt — beräkningsunderlag</t>
+          <t>Ej tryckt</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bildprompt (en)</t>
+          <t>Intäkt/kvm nu</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>namn_en</t>
+          <t>intäkt/kvm nu</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -13339,27 +13657,71 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ej tryckt — underlag för bildgenerering</t>
+          <t>Ej tryckt — beräkningsunderlag</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>Förslag intäkt</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>förslag intäkt</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Ej tryckt — beräkningsunderlag</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Bildprompt (en)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>namn_en</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Nej</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Ej tryckt — underlag för bildgenerering</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>Antal exemplar</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Nej</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Antal tryckta kort (utskrift_config: 1)</t>
         </is>
@@ -13376,7 +13738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13566,10 +13928,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Omräkning 2026-09-27</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>MV × 1,3/1,4/1,5 (kolumn MV-faktor), ränta 2 %, lån 70 % av anskaffningen; kort med högre faktor fick motvikter (kolumn Motvikt).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Byggd med</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>verktyg/bygg_pu_projekt_excel.py</t>
         </is>
